--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="147">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,207 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>Internacional de Bogotá</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Al Ahli (QAT)</t>
+  </si>
+  <si>
+    <t>Al Riyadh SC</t>
+  </si>
+  <si>
+    <t>Qatar SC</t>
+  </si>
+  <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
+    <t>Racing Santander</t>
+  </si>
+  <si>
+    <t>Al Nassr</t>
+  </si>
+  <si>
+    <t>Al-Khaleej Saihat</t>
+  </si>
+  <si>
+    <t>Tamworth FC</t>
+  </si>
+  <si>
+    <t>Gateshead</t>
+  </si>
+  <si>
+    <t>Aldershot</t>
+  </si>
+  <si>
+    <t>Wealdstone</t>
+  </si>
+  <si>
+    <t>AFC Fylde</t>
+  </si>
+  <si>
+    <t>Altrincham</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Southend</t>
+  </si>
+  <si>
+    <t>Hartlepool</t>
+  </si>
+  <si>
+    <t>Scunthorpe</t>
+  </si>
+  <si>
+    <t>Hornchurch</t>
+  </si>
+  <si>
+    <t>Alaves</t>
+  </si>
+  <si>
+    <t>JS El Biar</t>
+  </si>
+  <si>
+    <t>Tolima</t>
+  </si>
+  <si>
+    <t>Deportivo Pasto</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Lusail</t>
+  </si>
+  <si>
+    <t>NEOM Sports Club</t>
+  </si>
+  <si>
+    <t>Al-Sadd</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Elche</t>
+  </si>
+  <si>
+    <t>Al-Taawoun Buraidah</t>
+  </si>
+  <si>
+    <t>Al-Hilal</t>
+  </si>
+  <si>
+    <t>Worthing</t>
+  </si>
+  <si>
+    <t>Sutton Utd</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Carlisle</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>FC Halifax Town</t>
+  </si>
+  <si>
+    <t>Yeovil</t>
+  </si>
+  <si>
+    <t>Kidderminster</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Solihull Moors</t>
+  </si>
+  <si>
+    <t>Woking</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Olympique Akbou</t>
+  </si>
+  <si>
+    <t>2026-08-26 00:09:27</t>
   </si>
 </sst>
 </file>
@@ -585,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1029,5814 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2">
+        <v>1.41</v>
+      </c>
+      <c r="G2">
+        <v>110</v>
+      </c>
+      <c r="H2">
+        <v>1.41</v>
+      </c>
+      <c r="I2">
+        <v>870</v>
+      </c>
+      <c r="J2">
+        <v>1.74</v>
+      </c>
+      <c r="K2">
+        <v>500</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.01</v>
+      </c>
+      <c r="O2">
+        <v>1.34</v>
+      </c>
+      <c r="P2">
+        <v>1.25</v>
+      </c>
+      <c r="Q2">
+        <v>1.34</v>
+      </c>
+      <c r="R2">
+        <v>1.13</v>
+      </c>
+      <c r="S2">
+        <v>2.66</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>1.67</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3">
+        <v>1.9</v>
+      </c>
+      <c r="G3">
+        <v>2.34</v>
+      </c>
+      <c r="H3">
+        <v>4.3</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>2.22</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.92</v>
+      </c>
+      <c r="O3">
+        <v>1.44</v>
+      </c>
+      <c r="P3">
+        <v>1.53</v>
+      </c>
+      <c r="Q3">
+        <v>2.2</v>
+      </c>
+      <c r="R3">
+        <v>1.2</v>
+      </c>
+      <c r="S3">
+        <v>3.55</v>
+      </c>
+      <c r="T3">
+        <v>1.77</v>
+      </c>
+      <c r="U3">
+        <v>1.69</v>
+      </c>
+      <c r="V3">
+        <v>1.19</v>
+      </c>
+      <c r="W3">
+        <v>1.74</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.01</v>
+      </c>
+      <c r="AR3">
+        <v>1.01</v>
+      </c>
+      <c r="AS3">
+        <v>1.01</v>
+      </c>
+      <c r="AT3">
+        <v>1.01</v>
+      </c>
+      <c r="AU3">
+        <v>1.01</v>
+      </c>
+      <c r="AV3">
+        <v>1.01</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>1.01</v>
+      </c>
+      <c r="AY3">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3">
+        <v>1.01</v>
+      </c>
+      <c r="BA3">
+        <v>1.01</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>1.01</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4">
+        <v>2.56</v>
+      </c>
+      <c r="G4">
+        <v>3.15</v>
+      </c>
+      <c r="H4">
+        <v>3.1</v>
+      </c>
+      <c r="I4">
+        <v>4.1</v>
+      </c>
+      <c r="J4">
+        <v>2.6</v>
+      </c>
+      <c r="K4">
+        <v>3.5</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.38</v>
+      </c>
+      <c r="Q4">
+        <v>2.46</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5">
+        <v>1.01</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1.01</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1.01</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6">
+        <v>3.85</v>
+      </c>
+      <c r="G6">
+        <v>5.1</v>
+      </c>
+      <c r="H6">
+        <v>1.83</v>
+      </c>
+      <c r="I6">
+        <v>2.02</v>
+      </c>
+      <c r="J6">
+        <v>3.8</v>
+      </c>
+      <c r="K6">
+        <v>5.4</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.12</v>
+      </c>
+      <c r="Q6">
+        <v>1.67</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7">
+        <v>5.6</v>
+      </c>
+      <c r="G7">
+        <v>9.6</v>
+      </c>
+      <c r="H7">
+        <v>1.09</v>
+      </c>
+      <c r="I7">
+        <v>1.57</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>3.1</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8">
+        <v>3.5</v>
+      </c>
+      <c r="G8">
+        <v>3.95</v>
+      </c>
+      <c r="H8">
+        <v>2.46</v>
+      </c>
+      <c r="I8">
+        <v>2.84</v>
+      </c>
+      <c r="J8">
+        <v>2.78</v>
+      </c>
+      <c r="K8">
+        <v>3.25</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.42</v>
+      </c>
+      <c r="Q8">
+        <v>2.98</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G9">
+        <v>9.4</v>
+      </c>
+      <c r="H9">
+        <v>1.53</v>
+      </c>
+      <c r="I9">
+        <v>1.57</v>
+      </c>
+      <c r="J9">
+        <v>4.1</v>
+      </c>
+      <c r="K9">
+        <v>4.5</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.79</v>
+      </c>
+      <c r="Q9">
+        <v>2.08</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>2.22</v>
+      </c>
+      <c r="G10">
+        <v>2.26</v>
+      </c>
+      <c r="H10">
+        <v>3.5</v>
+      </c>
+      <c r="I10">
+        <v>3.65</v>
+      </c>
+      <c r="J10">
+        <v>3.6</v>
+      </c>
+      <c r="K10">
+        <v>3.65</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>4.2</v>
+      </c>
+      <c r="O10">
+        <v>1.28</v>
+      </c>
+      <c r="P10">
+        <v>2.12</v>
+      </c>
+      <c r="Q10">
+        <v>1.85</v>
+      </c>
+      <c r="R10">
+        <v>1.42</v>
+      </c>
+      <c r="S10">
+        <v>3.1</v>
+      </c>
+      <c r="T10">
+        <v>1.68</v>
+      </c>
+      <c r="U10">
+        <v>2.36</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>17</v>
+      </c>
+      <c r="Y10">
+        <v>15.5</v>
+      </c>
+      <c r="Z10">
+        <v>28</v>
+      </c>
+      <c r="AA10">
+        <v>75</v>
+      </c>
+      <c r="AB10">
+        <v>11.5</v>
+      </c>
+      <c r="AC10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>14.5</v>
+      </c>
+      <c r="AE10">
+        <v>40</v>
+      </c>
+      <c r="AF10">
+        <v>16</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>16</v>
+      </c>
+      <c r="AI10">
+        <v>46</v>
+      </c>
+      <c r="AJ10">
+        <v>32</v>
+      </c>
+      <c r="AK10">
+        <v>23</v>
+      </c>
+      <c r="AL10">
+        <v>34</v>
+      </c>
+      <c r="AM10">
+        <v>90</v>
+      </c>
+      <c r="AN10">
+        <v>16.5</v>
+      </c>
+      <c r="AO10">
+        <v>36</v>
+      </c>
+      <c r="AP10">
+        <v>15</v>
+      </c>
+      <c r="AQ10">
+        <v>13.5</v>
+      </c>
+      <c r="AR10">
+        <v>18</v>
+      </c>
+      <c r="AS10">
+        <v>30</v>
+      </c>
+      <c r="AT10">
+        <v>10</v>
+      </c>
+      <c r="AU10">
+        <v>7.4</v>
+      </c>
+      <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
+        <v>30</v>
+      </c>
+      <c r="AX10">
+        <v>13.5</v>
+      </c>
+      <c r="AY10">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10">
+        <v>14</v>
+      </c>
+      <c r="BA10">
+        <v>34</v>
+      </c>
+      <c r="BB10">
+        <v>19.5</v>
+      </c>
+      <c r="BC10">
+        <v>19.5</v>
+      </c>
+      <c r="BD10">
+        <v>21</v>
+      </c>
+      <c r="BE10">
+        <v>34</v>
+      </c>
+      <c r="BF10">
+        <v>14</v>
+      </c>
+      <c r="BG10">
+        <v>25</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11">
+        <v>1.29</v>
+      </c>
+      <c r="G11">
+        <v>1.45</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>5.1</v>
+      </c>
+      <c r="K11">
+        <v>12.5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.4</v>
+      </c>
+      <c r="Q11">
+        <v>1.39</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12">
+        <v>7.8</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.27</v>
+      </c>
+      <c r="I12">
+        <v>1.39</v>
+      </c>
+      <c r="J12">
+        <v>5.1</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.68</v>
+      </c>
+      <c r="Q12">
+        <v>1.41</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13">
+        <v>1.99</v>
+      </c>
+      <c r="G13">
+        <v>2.62</v>
+      </c>
+      <c r="H13">
+        <v>2.88</v>
+      </c>
+      <c r="I13">
+        <v>4.2</v>
+      </c>
+      <c r="J13">
+        <v>3.4</v>
+      </c>
+      <c r="K13">
+        <v>5.6</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.14</v>
+      </c>
+      <c r="Q13">
+        <v>1.49</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>26</v>
+      </c>
+      <c r="Z13">
+        <v>38</v>
+      </c>
+      <c r="AA13">
+        <v>75</v>
+      </c>
+      <c r="AB13">
+        <v>20</v>
+      </c>
+      <c r="AC13">
+        <v>14</v>
+      </c>
+      <c r="AD13">
+        <v>20</v>
+      </c>
+      <c r="AE13">
+        <v>46</v>
+      </c>
+      <c r="AF13">
+        <v>25</v>
+      </c>
+      <c r="AG13">
+        <v>16.5</v>
+      </c>
+      <c r="AH13">
+        <v>22</v>
+      </c>
+      <c r="AI13">
+        <v>50</v>
+      </c>
+      <c r="AJ13">
+        <v>42</v>
+      </c>
+      <c r="AK13">
+        <v>30</v>
+      </c>
+      <c r="AL13">
+        <v>42</v>
+      </c>
+      <c r="AM13">
+        <v>85</v>
+      </c>
+      <c r="AN13">
+        <v>17</v>
+      </c>
+      <c r="AO13">
+        <v>32</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>11</v>
+      </c>
+      <c r="AR13">
+        <v>16</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>8.6</v>
+      </c>
+      <c r="AU13">
+        <v>6.2</v>
+      </c>
+      <c r="AV13">
+        <v>9</v>
+      </c>
+      <c r="AW13">
+        <v>19.5</v>
+      </c>
+      <c r="AX13">
+        <v>11</v>
+      </c>
+      <c r="AY13">
+        <v>7.2</v>
+      </c>
+      <c r="AZ13">
+        <v>9.4</v>
+      </c>
+      <c r="BA13">
+        <v>1.03</v>
+      </c>
+      <c r="BB13">
+        <v>17</v>
+      </c>
+      <c r="BC13">
+        <v>13</v>
+      </c>
+      <c r="BD13">
+        <v>17</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>7.4</v>
+      </c>
+      <c r="BG13">
+        <v>13.5</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14">
+        <v>2.82</v>
+      </c>
+      <c r="G14">
+        <v>3.1</v>
+      </c>
+      <c r="H14">
+        <v>2.42</v>
+      </c>
+      <c r="I14">
+        <v>2.68</v>
+      </c>
+      <c r="J14">
+        <v>3.55</v>
+      </c>
+      <c r="K14">
+        <v>4.1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.08</v>
+      </c>
+      <c r="Q14">
+        <v>1.7</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15">
+        <v>3.25</v>
+      </c>
+      <c r="G15">
+        <v>3.9</v>
+      </c>
+      <c r="H15">
+        <v>1.83</v>
+      </c>
+      <c r="I15">
+        <v>2.34</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>5.6</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>2.08</v>
+      </c>
+      <c r="Q15">
+        <v>1.58</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16">
+        <v>3.05</v>
+      </c>
+      <c r="G16">
+        <v>3.55</v>
+      </c>
+      <c r="H16">
+        <v>2.1</v>
+      </c>
+      <c r="I16">
+        <v>2.38</v>
+      </c>
+      <c r="J16">
+        <v>3.85</v>
+      </c>
+      <c r="K16">
+        <v>4.4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.32</v>
+      </c>
+      <c r="Q16">
+        <v>1.56</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17">
+        <v>2.76</v>
+      </c>
+      <c r="G17">
+        <v>3.15</v>
+      </c>
+      <c r="H17">
+        <v>2.26</v>
+      </c>
+      <c r="I17">
+        <v>2.54</v>
+      </c>
+      <c r="J17">
+        <v>3.85</v>
+      </c>
+      <c r="K17">
+        <v>4.6</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.64</v>
+      </c>
+      <c r="Q17">
+        <v>1.5</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18">
+        <v>2.32</v>
+      </c>
+      <c r="G18">
+        <v>2.96</v>
+      </c>
+      <c r="H18">
+        <v>2.56</v>
+      </c>
+      <c r="I18">
+        <v>3.8</v>
+      </c>
+      <c r="J18">
+        <v>3.15</v>
+      </c>
+      <c r="K18">
+        <v>5.7</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.88</v>
+      </c>
+      <c r="Q18">
+        <v>1.67</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19">
+        <v>1.88</v>
+      </c>
+      <c r="G19">
+        <v>2.04</v>
+      </c>
+      <c r="H19">
+        <v>4.5</v>
+      </c>
+      <c r="I19">
+        <v>5.1</v>
+      </c>
+      <c r="J19">
+        <v>3.35</v>
+      </c>
+      <c r="K19">
+        <v>3.8</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1.62</v>
+      </c>
+      <c r="Q19">
+        <v>2.1</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20">
+        <v>1.54</v>
+      </c>
+      <c r="G20">
+        <v>1.6</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>4.1</v>
+      </c>
+      <c r="K20">
+        <v>4.9</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1.89</v>
+      </c>
+      <c r="Q20">
+        <v>1.65</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21">
+        <v>1.86</v>
+      </c>
+      <c r="G21">
+        <v>2.02</v>
+      </c>
+      <c r="H21">
+        <v>4.2</v>
+      </c>
+      <c r="I21">
+        <v>4.9</v>
+      </c>
+      <c r="J21">
+        <v>3.6</v>
+      </c>
+      <c r="K21">
+        <v>4.1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.82</v>
+      </c>
+      <c r="Q21">
+        <v>1.8</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22">
+        <v>1.75</v>
+      </c>
+      <c r="G22">
+        <v>1.91</v>
+      </c>
+      <c r="H22">
+        <v>4.3</v>
+      </c>
+      <c r="I22">
+        <v>4.9</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4.6</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.1</v>
+      </c>
+      <c r="Q22">
+        <v>1.52</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23">
+        <v>2.32</v>
+      </c>
+      <c r="G23">
+        <v>2.58</v>
+      </c>
+      <c r="H23">
+        <v>2.94</v>
+      </c>
+      <c r="I23">
+        <v>3.4</v>
+      </c>
+      <c r="J23">
+        <v>3.45</v>
+      </c>
+      <c r="K23">
+        <v>3.9</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.81</v>
+      </c>
+      <c r="Q23">
+        <v>1.72</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24">
+        <v>3.2</v>
+      </c>
+      <c r="G24">
+        <v>3.3</v>
+      </c>
+      <c r="H24">
+        <v>2.36</v>
+      </c>
+      <c r="I24">
+        <v>2.4</v>
+      </c>
+      <c r="J24">
+        <v>3.6</v>
+      </c>
+      <c r="K24">
+        <v>3.7</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.06</v>
+      </c>
+      <c r="N24">
+        <v>4.2</v>
+      </c>
+      <c r="O24">
+        <v>1.29</v>
+      </c>
+      <c r="P24">
+        <v>2.1</v>
+      </c>
+      <c r="Q24">
+        <v>1.86</v>
+      </c>
+      <c r="R24">
+        <v>1.41</v>
+      </c>
+      <c r="S24">
+        <v>3.2</v>
+      </c>
+      <c r="T24">
+        <v>1.7</v>
+      </c>
+      <c r="U24">
+        <v>2.34</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>17</v>
+      </c>
+      <c r="Y24">
+        <v>11.5</v>
+      </c>
+      <c r="Z24">
+        <v>16</v>
+      </c>
+      <c r="AA24">
+        <v>34</v>
+      </c>
+      <c r="AB24">
+        <v>14</v>
+      </c>
+      <c r="AC24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD24">
+        <v>11</v>
+      </c>
+      <c r="AE24">
+        <v>25</v>
+      </c>
+      <c r="AF24">
+        <v>24</v>
+      </c>
+      <c r="AG24">
+        <v>14</v>
+      </c>
+      <c r="AH24">
+        <v>16.5</v>
+      </c>
+      <c r="AI24">
+        <v>38</v>
+      </c>
+      <c r="AJ24">
+        <v>60</v>
+      </c>
+      <c r="AK24">
+        <v>38</v>
+      </c>
+      <c r="AL24">
+        <v>46</v>
+      </c>
+      <c r="AM24">
+        <v>85</v>
+      </c>
+      <c r="AN24">
+        <v>32</v>
+      </c>
+      <c r="AO24">
+        <v>18</v>
+      </c>
+      <c r="AP24">
+        <v>15</v>
+      </c>
+      <c r="AQ24">
+        <v>10</v>
+      </c>
+      <c r="AR24">
+        <v>14</v>
+      </c>
+      <c r="AS24">
+        <v>21</v>
+      </c>
+      <c r="AT24">
+        <v>12.5</v>
+      </c>
+      <c r="AU24">
+        <v>7.4</v>
+      </c>
+      <c r="AV24">
+        <v>10</v>
+      </c>
+      <c r="AW24">
+        <v>20</v>
+      </c>
+      <c r="AX24">
+        <v>20</v>
+      </c>
+      <c r="AY24">
+        <v>12.5</v>
+      </c>
+      <c r="AZ24">
+        <v>14.5</v>
+      </c>
+      <c r="BA24">
+        <v>22</v>
+      </c>
+      <c r="BB24">
+        <v>28</v>
+      </c>
+      <c r="BC24">
+        <v>29</v>
+      </c>
+      <c r="BD24">
+        <v>25</v>
+      </c>
+      <c r="BE24">
+        <v>34</v>
+      </c>
+      <c r="BF24">
+        <v>19</v>
+      </c>
+      <c r="BG24">
+        <v>16</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25">
+        <v>1.04</v>
+      </c>
+      <c r="G25">
+        <v>1000</v>
+      </c>
+      <c r="H25">
+        <v>1.04</v>
+      </c>
+      <c r="I25">
+        <v>1000</v>
+      </c>
+      <c r="J25">
+        <v>1.04</v>
+      </c>
+      <c r="K25">
+        <v>950</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.01</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="151">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Saudi 1st Division</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>15:50:00</t>
   </si>
   <si>
+    <t>15:55:00</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -325,18 +331,21 @@
     <t>Al Riyadh SC</t>
   </si>
   <si>
+    <t>Al-Anwar Club</t>
+  </si>
+  <si>
     <t>Qatar SC</t>
   </si>
   <si>
+    <t>Racing Santander</t>
+  </si>
+  <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
     <t>Al Ittihad (EGY)</t>
   </si>
   <si>
-    <t>ZED FC</t>
-  </si>
-  <si>
-    <t>Racing Santander</t>
-  </si>
-  <si>
     <t>Al Nassr</t>
   </si>
   <si>
@@ -397,18 +406,21 @@
     <t>NEOM Sports Club</t>
   </si>
   <si>
+    <t>Al-Ula FC</t>
+  </si>
+  <si>
     <t>Al-Sadd</t>
   </si>
   <si>
+    <t>Elche</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Al Ahly Cairo</t>
-  </si>
-  <si>
-    <t>Elche</t>
-  </si>
-  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
@@ -454,7 +466,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-08-26 00:09:27</t>
+    <t>2026-08-26 02:18:24</t>
   </si>
 </sst>
 </file>
@@ -786,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1036,16 +1048,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>1.41</v>
@@ -1081,13 +1093,13 @@
         <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="R2">
         <v>1.13</v>
       </c>
       <c r="S2">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1270,7 +1282,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1278,34 +1290,34 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F3">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G3">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1314,16 +1326,16 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
         <v>1.2</v>
@@ -1338,10 +1350,10 @@
         <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1512,7 +1524,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1520,34 +1532,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G4">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="J4">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1754,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1762,31 +1774,31 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H5">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1804,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1996,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2004,22 +2016,22 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F6">
         <v>3.85</v>
       </c>
       <c r="G6">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H6">
         <v>1.83</v>
@@ -2238,39 +2250,39 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>1.57</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2288,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
         <v>1.01</v>
@@ -2480,42 +2492,42 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="G8">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="H8">
-        <v>2.46</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
-        <v>2.84</v>
+        <v>1.57</v>
       </c>
       <c r="J8">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2530,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.42</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2722,314 +2734,314 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F9">
+        <v>2.22</v>
+      </c>
+      <c r="G9">
+        <v>2.26</v>
+      </c>
+      <c r="H9">
+        <v>3.5</v>
+      </c>
+      <c r="I9">
+        <v>3.6</v>
+      </c>
+      <c r="J9">
+        <v>3.6</v>
+      </c>
+      <c r="K9">
+        <v>3.65</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1.06</v>
+      </c>
+      <c r="N9">
+        <v>4.2</v>
+      </c>
+      <c r="O9">
+        <v>1.28</v>
+      </c>
+      <c r="P9">
+        <v>2.12</v>
+      </c>
+      <c r="Q9">
+        <v>1.85</v>
+      </c>
+      <c r="R9">
+        <v>1.42</v>
+      </c>
+      <c r="S9">
+        <v>3.1</v>
+      </c>
+      <c r="T9">
+        <v>1.68</v>
+      </c>
+      <c r="U9">
+        <v>2.36</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>16.5</v>
+      </c>
+      <c r="Y9">
+        <v>15.5</v>
+      </c>
+      <c r="Z9">
+        <v>28</v>
+      </c>
+      <c r="AA9">
+        <v>75</v>
+      </c>
+      <c r="AB9">
+        <v>11.5</v>
+      </c>
+      <c r="AC9">
         <v>8.199999999999999</v>
       </c>
-      <c r="G9">
-        <v>9.4</v>
-      </c>
-      <c r="H9">
-        <v>1.53</v>
-      </c>
-      <c r="I9">
-        <v>1.57</v>
-      </c>
-      <c r="J9">
-        <v>4.1</v>
-      </c>
-      <c r="K9">
-        <v>4.5</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1.79</v>
-      </c>
-      <c r="Q9">
-        <v>2.08</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
       <c r="AD9">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>2.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10">
-        <v>2.26</v>
+        <v>9.4</v>
       </c>
       <c r="H10">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="I10">
-        <v>3.65</v>
+        <v>1.56</v>
       </c>
       <c r="J10">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -3038,210 +3050,210 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BG10">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="G11">
-        <v>1.45</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>2.46</v>
       </c>
       <c r="I11">
-        <v>42</v>
+        <v>2.84</v>
       </c>
       <c r="J11">
-        <v>5.1</v>
+        <v>2.78</v>
       </c>
       <c r="K11">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3256,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q11">
-        <v>1.39</v>
+        <v>2.98</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3448,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3456,34 +3468,34 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>7.8</v>
+        <v>1.34</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>1.43</v>
       </c>
       <c r="H12">
-        <v>1.27</v>
+        <v>8.4</v>
       </c>
       <c r="I12">
-        <v>1.39</v>
+        <v>10.5</v>
       </c>
       <c r="J12">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3498,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q12">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3510,10 +3522,10 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3522,112 +3534,112 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12">
         <v>0</v>
@@ -3690,48 +3702,48 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>1.99</v>
+        <v>7.8</v>
       </c>
       <c r="G13">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>2.88</v>
+        <v>1.23</v>
       </c>
       <c r="I13">
-        <v>4.2</v>
+        <v>1.39</v>
       </c>
       <c r="J13">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="K13">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3740,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="Q13">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3752,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3767,109 +3779,109 @@
         <v>1000</v>
       </c>
       <c r="Y13">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
         <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
         <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>0</v>
@@ -3932,186 +3944,186 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14">
+        <v>1.99</v>
+      </c>
+      <c r="G14">
+        <v>2.62</v>
+      </c>
+      <c r="H14">
+        <v>2.88</v>
+      </c>
+      <c r="I14">
+        <v>4.2</v>
+      </c>
+      <c r="J14">
+        <v>3.4</v>
+      </c>
+      <c r="K14">
+        <v>4.3</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.14</v>
+      </c>
+      <c r="Q14">
+        <v>1.49</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>26</v>
+      </c>
+      <c r="Z14">
+        <v>38</v>
+      </c>
+      <c r="AA14">
+        <v>75</v>
+      </c>
+      <c r="AB14">
+        <v>20</v>
+      </c>
+      <c r="AC14">
+        <v>14</v>
+      </c>
+      <c r="AD14">
+        <v>20</v>
+      </c>
+      <c r="AE14">
+        <v>46</v>
+      </c>
+      <c r="AF14">
+        <v>25</v>
+      </c>
+      <c r="AG14">
+        <v>16.5</v>
+      </c>
+      <c r="AH14">
+        <v>22</v>
+      </c>
+      <c r="AI14">
+        <v>50</v>
+      </c>
+      <c r="AJ14">
+        <v>42</v>
+      </c>
+      <c r="AK14">
+        <v>30</v>
+      </c>
+      <c r="AL14">
+        <v>42</v>
+      </c>
+      <c r="AM14">
         <v>85</v>
       </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14">
-        <v>2.82</v>
-      </c>
-      <c r="G14">
-        <v>3.1</v>
-      </c>
-      <c r="H14">
-        <v>2.42</v>
-      </c>
-      <c r="I14">
-        <v>2.68</v>
-      </c>
-      <c r="J14">
-        <v>3.55</v>
-      </c>
-      <c r="K14">
-        <v>4.1</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>2.08</v>
-      </c>
-      <c r="Q14">
-        <v>1.7</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
       <c r="AN14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4174,42 +4186,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="G15">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="H15">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="I15">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4227,7 +4239,7 @@
         <v>2.08</v>
       </c>
       <c r="Q15">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4416,42 +4428,42 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G16">
+        <v>3.9</v>
+      </c>
+      <c r="H16">
+        <v>1.83</v>
+      </c>
+      <c r="I16">
+        <v>2.34</v>
+      </c>
+      <c r="J16">
         <v>3.55</v>
       </c>
-      <c r="H16">
-        <v>2.1</v>
-      </c>
-      <c r="I16">
-        <v>2.38</v>
-      </c>
-      <c r="J16">
-        <v>3.85</v>
-      </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4466,10 +4478,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4658,42 +4670,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="G17">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="H17">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="I17">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="J17">
         <v>3.85</v>
       </c>
       <c r="K17">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4708,10 +4720,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="Q17">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4900,42 +4912,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F18">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="G18">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="H18">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="I18">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="J18">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4950,10 +4962,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.88</v>
+        <v>2.64</v>
       </c>
       <c r="Q18">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5142,60 +5154,60 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F19">
+        <v>2.32</v>
+      </c>
+      <c r="G19">
+        <v>2.96</v>
+      </c>
+      <c r="H19">
+        <v>2.56</v>
+      </c>
+      <c r="I19">
+        <v>3.8</v>
+      </c>
+      <c r="J19">
+        <v>3.15</v>
+      </c>
+      <c r="K19">
+        <v>5.7</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>1.88</v>
       </c>
-      <c r="G19">
-        <v>2.04</v>
-      </c>
-      <c r="H19">
-        <v>4.5</v>
-      </c>
-      <c r="I19">
-        <v>5.1</v>
-      </c>
-      <c r="J19">
-        <v>3.35</v>
-      </c>
-      <c r="K19">
-        <v>3.8</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>1.62</v>
-      </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5384,42 +5396,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F20">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="G20">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K20">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5434,10 +5446,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="Q20">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5626,43 +5638,43 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F21">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="G21">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="H21">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="I21">
+        <v>7.4</v>
+      </c>
+      <c r="J21">
+        <v>4.1</v>
+      </c>
+      <c r="K21">
         <v>4.9</v>
       </c>
-      <c r="J21">
-        <v>3.6</v>
-      </c>
-      <c r="K21">
-        <v>4.1</v>
-      </c>
       <c r="L21">
         <v>0</v>
       </c>
@@ -5676,10 +5688,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="Q21">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5868,42 +5880,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F22">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="G22">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="H22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I22">
         <v>4.9</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5918,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="Q22">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6110,42 +6122,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F23">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="G23">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
       <c r="H23">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="I23">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="J23">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6160,10 +6172,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6352,72 +6364,72 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F24">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="G24">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="H24">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="I24">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K24">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="Q24">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="R24">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -6426,417 +6438,659 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL24">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR24">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AU24">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AY24">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BB24">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BD24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF24">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BG24">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25">
+        <v>3.2</v>
+      </c>
+      <c r="G25">
+        <v>3.3</v>
+      </c>
+      <c r="H25">
+        <v>2.36</v>
+      </c>
+      <c r="I25">
+        <v>2.4</v>
+      </c>
+      <c r="J25">
+        <v>3.6</v>
+      </c>
+      <c r="K25">
+        <v>3.7</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1.06</v>
+      </c>
+      <c r="N25">
+        <v>4.2</v>
+      </c>
+      <c r="O25">
+        <v>1.29</v>
+      </c>
+      <c r="P25">
+        <v>2.1</v>
+      </c>
+      <c r="Q25">
+        <v>1.85</v>
+      </c>
+      <c r="R25">
+        <v>1.41</v>
+      </c>
+      <c r="S25">
+        <v>3.2</v>
+      </c>
+      <c r="T25">
+        <v>1.7</v>
+      </c>
+      <c r="U25">
+        <v>2.34</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>16.5</v>
+      </c>
+      <c r="Y25">
+        <v>11.5</v>
+      </c>
+      <c r="Z25">
+        <v>16</v>
+      </c>
+      <c r="AA25">
+        <v>34</v>
+      </c>
+      <c r="AB25">
+        <v>14</v>
+      </c>
+      <c r="AC25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD25">
+        <v>11</v>
+      </c>
+      <c r="AE25">
+        <v>25</v>
+      </c>
+      <c r="AF25">
+        <v>24</v>
+      </c>
+      <c r="AG25">
+        <v>14</v>
+      </c>
+      <c r="AH25">
+        <v>16.5</v>
+      </c>
+      <c r="AI25">
+        <v>38</v>
+      </c>
+      <c r="AJ25">
+        <v>60</v>
+      </c>
+      <c r="AK25">
+        <v>38</v>
+      </c>
+      <c r="AL25">
+        <v>46</v>
+      </c>
+      <c r="AM25">
+        <v>85</v>
+      </c>
+      <c r="AN25">
+        <v>32</v>
+      </c>
+      <c r="AO25">
+        <v>18</v>
+      </c>
+      <c r="AP25">
+        <v>15</v>
+      </c>
+      <c r="AQ25">
+        <v>10</v>
+      </c>
+      <c r="AR25">
+        <v>14</v>
+      </c>
+      <c r="AS25">
+        <v>21</v>
+      </c>
+      <c r="AT25">
+        <v>12.5</v>
+      </c>
+      <c r="AU25">
+        <v>7.4</v>
+      </c>
+      <c r="AV25">
+        <v>10</v>
+      </c>
+      <c r="AW25">
+        <v>20</v>
+      </c>
+      <c r="AX25">
+        <v>20</v>
+      </c>
+      <c r="AY25">
+        <v>12.5</v>
+      </c>
+      <c r="AZ25">
+        <v>14.5</v>
+      </c>
+      <c r="BA25">
+        <v>22</v>
+      </c>
+      <c r="BB25">
+        <v>28</v>
+      </c>
+      <c r="BC25">
+        <v>29</v>
+      </c>
+      <c r="BD25">
+        <v>25</v>
+      </c>
+      <c r="BE25">
+        <v>34</v>
+      </c>
+      <c r="BF25">
+        <v>19</v>
+      </c>
+      <c r="BG25">
+        <v>16</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>145</v>
-      </c>
-      <c r="F25">
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26">
         <v>1.04</v>
       </c>
-      <c r="G25">
-        <v>1000</v>
-      </c>
-      <c r="H25">
+      <c r="G26">
+        <v>1000</v>
+      </c>
+      <c r="H26">
         <v>1.04</v>
       </c>
-      <c r="I25">
-        <v>1000</v>
-      </c>
-      <c r="J25">
+      <c r="I26">
+        <v>1000</v>
+      </c>
+      <c r="J26">
         <v>1.04</v>
       </c>
-      <c r="K25">
+      <c r="K26">
         <v>950</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
         <v>1.24</v>
       </c>
-      <c r="Q25">
-        <v>1.01</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-      <c r="BF25">
-        <v>0</v>
-      </c>
-      <c r="BG25">
-        <v>0</v>
-      </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-      <c r="BI25">
-        <v>0</v>
-      </c>
-      <c r="BJ25">
-        <v>0</v>
-      </c>
-      <c r="BK25">
-        <v>0</v>
-      </c>
-      <c r="BL25">
-        <v>0</v>
-      </c>
-      <c r="BM25">
-        <v>0</v>
-      </c>
-      <c r="BN25">
-        <v>0</v>
-      </c>
-      <c r="BO25">
-        <v>0</v>
-      </c>
-      <c r="BP25">
-        <v>0</v>
-      </c>
-      <c r="BQ25">
-        <v>0</v>
-      </c>
-      <c r="BR25">
-        <v>0</v>
-      </c>
-      <c r="BS25">
-        <v>0</v>
-      </c>
-      <c r="BT25">
-        <v>0</v>
-      </c>
-      <c r="BU25">
-        <v>0</v>
-      </c>
-      <c r="BV25">
-        <v>0</v>
-      </c>
-      <c r="BW25">
-        <v>0</v>
-      </c>
-      <c r="BX25">
-        <v>0</v>
-      </c>
-      <c r="BY25">
-        <v>0</v>
-      </c>
-      <c r="BZ25">
-        <v>0</v>
-      </c>
-      <c r="CA25">
-        <v>0</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>146</v>
+      <c r="Q26">
+        <v>1.01</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -466,7 +466,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-08-26 02:18:24</t>
+    <t>2026-08-26 03:53:56</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1072,7 @@
         <v>870</v>
       </c>
       <c r="J2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="K2">
         <v>500</v>
@@ -1326,13 +1326,13 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
         <v>2.32</v>
@@ -1344,13 +1344,13 @@
         <v>3.55</v>
       </c>
       <c r="T3">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
         <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
         <v>1.9</v>
@@ -1789,7 +1789,7 @@
         <v>1.55</v>
       </c>
       <c r="G5">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="H5">
         <v>3.8</v>
@@ -2028,10 +2028,10 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G6">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
         <v>1.83</v>
@@ -2043,7 +2043,7 @@
         <v>3.8</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2058,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R9">
         <v>1.42</v>
@@ -2904,7 +2904,7 @@
         <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE9">
         <v>34</v>
@@ -2916,61 +2916,61 @@
         <v>25</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9">
         <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9">
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
@@ -3483,7 +3483,7 @@
         <v>1.34</v>
       </c>
       <c r="G12">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H12">
         <v>8.4</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q12">
         <v>1.46</v>
@@ -3722,22 +3722,22 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="H13">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="I13">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="J13">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="K13">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q13">
         <v>1.41</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3776,112 +3776,112 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH13">
         <v>0</v>
@@ -3964,22 +3964,22 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H14">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3994,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4018,112 +4018,112 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y14">
+        <v>22</v>
+      </c>
+      <c r="Z14">
+        <v>32</v>
+      </c>
+      <c r="AA14">
+        <v>65</v>
+      </c>
+      <c r="AB14">
+        <v>17</v>
+      </c>
+      <c r="AC14">
+        <v>12</v>
+      </c>
+      <c r="AD14">
+        <v>17.5</v>
+      </c>
+      <c r="AE14">
+        <v>40</v>
+      </c>
+      <c r="AF14">
+        <v>21</v>
+      </c>
+      <c r="AG14">
+        <v>14</v>
+      </c>
+      <c r="AH14">
+        <v>18.5</v>
+      </c>
+      <c r="AI14">
+        <v>44</v>
+      </c>
+      <c r="AJ14">
+        <v>36</v>
+      </c>
+      <c r="AK14">
         <v>26</v>
       </c>
-      <c r="Z14">
-        <v>38</v>
-      </c>
-      <c r="AA14">
+      <c r="AL14">
+        <v>36</v>
+      </c>
+      <c r="AM14">
         <v>75</v>
       </c>
-      <c r="AB14">
-        <v>20</v>
-      </c>
-      <c r="AC14">
+      <c r="AN14">
         <v>14</v>
       </c>
-      <c r="AD14">
-        <v>20</v>
-      </c>
-      <c r="AE14">
-        <v>46</v>
-      </c>
-      <c r="AF14">
-        <v>25</v>
-      </c>
-      <c r="AG14">
+      <c r="AO14">
+        <v>27</v>
+      </c>
+      <c r="AP14">
         <v>16.5</v>
       </c>
-      <c r="AH14">
-        <v>22</v>
-      </c>
-      <c r="AI14">
-        <v>50</v>
-      </c>
-      <c r="AJ14">
-        <v>42</v>
-      </c>
-      <c r="AK14">
-        <v>30</v>
-      </c>
-      <c r="AL14">
-        <v>42</v>
-      </c>
-      <c r="AM14">
-        <v>85</v>
-      </c>
-      <c r="AN14">
-        <v>17</v>
-      </c>
-      <c r="AO14">
-        <v>32</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
       <c r="AQ14">
+        <v>13</v>
+      </c>
+      <c r="AR14">
+        <v>19</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>10</v>
+      </c>
+      <c r="AU14">
+        <v>7.2</v>
+      </c>
+      <c r="AV14">
+        <v>10.5</v>
+      </c>
+      <c r="AW14">
+        <v>1.03</v>
+      </c>
+      <c r="AX14">
+        <v>12.5</v>
+      </c>
+      <c r="AY14">
+        <v>8.4</v>
+      </c>
+      <c r="AZ14">
         <v>11</v>
-      </c>
-      <c r="AR14">
-        <v>16</v>
-      </c>
-      <c r="AS14">
-        <v>1.01</v>
-      </c>
-      <c r="AT14">
-        <v>8.6</v>
-      </c>
-      <c r="AU14">
-        <v>6.2</v>
-      </c>
-      <c r="AV14">
-        <v>9</v>
-      </c>
-      <c r="AW14">
-        <v>19.5</v>
-      </c>
-      <c r="AX14">
-        <v>11</v>
-      </c>
-      <c r="AY14">
-        <v>7.2</v>
-      </c>
-      <c r="AZ14">
-        <v>9.4</v>
       </c>
       <c r="BA14">
         <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BE14">
         <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG14">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4236,10 +4236,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4448,22 +4448,22 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="G16">
         <v>3.9</v>
       </c>
       <c r="H16">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="I16">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4478,10 +4478,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q16">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4720,10 +4720,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4944,7 +4944,7 @@
         <v>2.54</v>
       </c>
       <c r="J18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
         <v>4.6</v>
@@ -5930,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q22">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>2.62</v>
       </c>
       <c r="H24">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I24">
         <v>3.9</v>
@@ -6632,10 +6632,10 @@
         <v>3.3</v>
       </c>
       <c r="H25">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I25">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J25">
         <v>3.6</v>
@@ -6671,7 +6671,7 @@
         <v>1.7</v>
       </c>
       <c r="U25">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -6737,7 +6737,7 @@
         <v>15</v>
       </c>
       <c r="AQ25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR25">
         <v>14</v>
@@ -6782,7 +6782,7 @@
         <v>34</v>
       </c>
       <c r="BF25">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG25">
         <v>16</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -466,7 +466,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:56</t>
+    <t>2026-08-26 06:03:53</t>
   </si>
 </sst>
 </file>
@@ -1060,22 +1060,22 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G2">
         <v>110</v>
       </c>
       <c r="H2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I2">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J2">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="K2">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1084,7 +1084,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
         <v>1.34</v>
@@ -1099,16 +1099,16 @@
         <v>1.13</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>1.05</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2">
         <v>1.67</v>
@@ -1225,61 +1225,61 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>150</v>
@@ -1302,58 +1302,58 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="G3">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>990</v>
       </c>
       <c r="J3">
-        <v>2.76</v>
+        <v>1.32</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1467,61 +1467,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>150</v>
@@ -1544,22 +1544,22 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G4">
-        <v>2.84</v>
+        <v>16.5</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>1.38</v>
       </c>
       <c r="Q4">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="G5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>15.5</v>
+        <v>5.7</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2028,22 +2028,22 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="G6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="I6">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2058,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2515,10 +2515,10 @@
         <v>5.6</v>
       </c>
       <c r="G8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="I8">
         <v>1.57</v>
@@ -2527,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
         <v>1.01</v>
@@ -2763,7 +2763,7 @@
         <v>3.5</v>
       </c>
       <c r="I9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J9">
         <v>3.6</v>
@@ -2784,22 +2784,22 @@
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
         <v>1.68</v>
       </c>
       <c r="U9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2811,40 +2811,40 @@
         <v>16.5</v>
       </c>
       <c r="Y9">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z9">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AA9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC9">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD9">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE9">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AF9">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AH9">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AI9">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AJ9">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AK9">
         <v>23</v>
@@ -2853,28 +2853,28 @@
         <v>34</v>
       </c>
       <c r="AM9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AO9">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS9">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
@@ -2883,97 +2883,97 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>30</v>
+        <v>4.3</v>
       </c>
       <c r="AX9">
         <v>13.5</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA9">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="BB9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC9">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BD9">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="BE9">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="BF9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG9">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BH9">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>150</v>
@@ -2996,22 +2996,22 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>8.199999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="G10">
-        <v>9.4</v>
+        <v>600</v>
       </c>
       <c r="H10">
         <v>1.53</v>
       </c>
       <c r="I10">
-        <v>1.56</v>
+        <v>870</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>1.06</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3238,22 +3238,22 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>600</v>
       </c>
       <c r="H11">
-        <v>2.46</v>
+        <v>1.08</v>
       </c>
       <c r="I11">
-        <v>2.84</v>
+        <v>870</v>
       </c>
       <c r="J11">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3268,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q11">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3480,22 +3480,22 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>1.42</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="I12">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>5.4</v>
+        <v>1.06</v>
       </c>
       <c r="K12">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>2.72</v>
       </c>
       <c r="Q12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3722,22 +3722,22 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="G13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="J13">
-        <v>5.9</v>
+        <v>1.11</v>
       </c>
       <c r="K13">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3752,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3776,112 +3776,112 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>0</v>
@@ -3964,19 +3964,19 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="G14">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
         <v>4.4</v>
@@ -3994,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>1.12</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4206,22 +4206,22 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>2.82</v>
+        <v>1.33</v>
       </c>
       <c r="G15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H15">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="I15">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>1.6</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4236,10 +4236,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.12</v>
+        <v>1.1</v>
       </c>
       <c r="Q15">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4448,22 +4448,22 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="G16">
         <v>3.9</v>
       </c>
       <c r="H16">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="I16">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="J16">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4478,10 +4478,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q16">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>3.1</v>
       </c>
       <c r="G17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H17">
         <v>2.1</v>
@@ -4705,7 +4705,7 @@
         <v>3.85</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4723,7 +4723,7 @@
         <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4932,22 +4932,22 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="G18">
-        <v>3.15</v>
+        <v>600</v>
       </c>
       <c r="H18">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="I18">
-        <v>2.54</v>
+        <v>870</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>1.06</v>
       </c>
       <c r="K18">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4962,10 +4962,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5177,19 +5177,19 @@
         <v>2.32</v>
       </c>
       <c r="G19">
-        <v>2.96</v>
+        <v>600</v>
       </c>
       <c r="H19">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="I19">
-        <v>3.8</v>
+        <v>870</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>1.51</v>
       </c>
       <c r="K19">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5204,10 +5204,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5416,19 +5416,19 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="G20">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H20">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>60</v>
       </c>
       <c r="J20">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K20">
         <v>3.75</v>
@@ -5446,10 +5446,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Q20">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5658,22 +5658,22 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="G21">
         <v>1.6</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="K21">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q21">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5900,19 +5900,19 @@
         <v>145</v>
       </c>
       <c r="F22">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="G22">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H22">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="I22">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
         <v>4.1</v>
@@ -5930,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="Q22">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6142,22 +6142,22 @@
         <v>146</v>
       </c>
       <c r="F23">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G23">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6172,10 +6172,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="Q23">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6384,22 +6384,22 @@
         <v>147</v>
       </c>
       <c r="F24">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G24">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H24">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="I24">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="J24">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K24">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.81</v>
+        <v>1.1</v>
       </c>
       <c r="Q24">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6626,16 +6626,16 @@
         <v>148</v>
       </c>
       <c r="F25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G25">
         <v>3.3</v>
       </c>
       <c r="H25">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I25">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J25">
         <v>3.6</v>
@@ -6653,7 +6653,7 @@
         <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P25">
         <v>2.1</v>
@@ -6665,13 +6665,13 @@
         <v>1.41</v>
       </c>
       <c r="S25">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T25">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U25">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -6683,55 +6683,55 @@
         <v>16.5</v>
       </c>
       <c r="Y25">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="Z25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA25">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC25">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD25">
         <v>11</v>
       </c>
       <c r="AE25">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH25">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI25">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ25">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="AK25">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL25">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP25">
         <v>15</v>
@@ -6740,13 +6740,13 @@
         <v>10.5</v>
       </c>
       <c r="AR25">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AS25">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AT25">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU25">
         <v>7.4</v>
@@ -6755,97 +6755,97 @@
         <v>10</v>
       </c>
       <c r="AW25">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AX25">
         <v>20</v>
       </c>
       <c r="AY25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
         <v>14.5</v>
       </c>
       <c r="BA25">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BB25">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC25">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="BD25">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="BE25">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BF25">
         <v>19.5</v>
       </c>
       <c r="BG25">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>150</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="157">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>South Korean K2 League</t>
+  </si>
+  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
@@ -286,6 +289,9 @@
     <t>01:15:00</t>
   </si>
   <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -322,6 +328,12 @@
     <t>Internacional de Bogotá</t>
   </si>
   <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Ansan Greeners FC</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
@@ -337,54 +349,54 @@
     <t>Qatar SC</t>
   </si>
   <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
     <t>Racing Santander</t>
   </si>
   <si>
-    <t>ZED FC</t>
-  </si>
-  <si>
-    <t>Al Ittihad (EGY)</t>
+    <t>Al-Khaleej Saihat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>Al-Khaleej Saihat</t>
+    <t>Altrincham</t>
+  </si>
+  <si>
+    <t>Scunthorpe</t>
+  </si>
+  <si>
+    <t>Hartlepool</t>
+  </si>
+  <si>
+    <t>Southend</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Hornchurch</t>
+  </si>
+  <si>
+    <t>AFC Fylde</t>
+  </si>
+  <si>
+    <t>Wealdstone</t>
+  </si>
+  <si>
+    <t>Aldershot</t>
+  </si>
+  <si>
+    <t>Gateshead</t>
   </si>
   <si>
     <t>Tamworth FC</t>
   </si>
   <si>
-    <t>Gateshead</t>
-  </si>
-  <si>
-    <t>Aldershot</t>
-  </si>
-  <si>
-    <t>Wealdstone</t>
-  </si>
-  <si>
-    <t>AFC Fylde</t>
-  </si>
-  <si>
-    <t>Altrincham</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Southend</t>
-  </si>
-  <si>
-    <t>Hartlepool</t>
-  </si>
-  <si>
-    <t>Scunthorpe</t>
-  </si>
-  <si>
-    <t>Hornchurch</t>
-  </si>
-  <si>
     <t>Alaves</t>
   </si>
   <si>
@@ -397,6 +409,12 @@
     <t>Deportivo Pasto</t>
   </si>
   <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Daegu Fc</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
@@ -412,61 +430,61 @@
     <t>Al-Sadd</t>
   </si>
   <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
     <t>Elche</t>
   </si>
   <si>
-    <t>Al Ahly Cairo</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
+    <t>Al-Hilal</t>
   </si>
   <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
-    <t>Al-Hilal</t>
+    <t>FC Halifax Town</t>
+  </si>
+  <si>
+    <t>Solihull Moors</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Kidderminster</t>
+  </si>
+  <si>
+    <t>Yeovil</t>
+  </si>
+  <si>
+    <t>Woking</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>Carlisle</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Sutton Utd</t>
   </si>
   <si>
     <t>Worthing</t>
   </si>
   <si>
-    <t>Sutton Utd</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Carlisle</t>
-  </si>
-  <si>
-    <t>Forest Green</t>
-  </si>
-  <si>
-    <t>FC Halifax Town</t>
-  </si>
-  <si>
-    <t>Yeovil</t>
-  </si>
-  <si>
-    <t>Kidderminster</t>
-  </si>
-  <si>
-    <t>Eastleigh</t>
-  </si>
-  <si>
-    <t>Solihull Moors</t>
-  </si>
-  <si>
-    <t>Woking</t>
-  </si>
-  <si>
     <t>Villarreal</t>
   </si>
   <si>
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-08-26 06:03:53</t>
+    <t>2026-08-26 08:13:39</t>
   </si>
 </sst>
 </file>
@@ -798,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1048,34 +1066,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="G2">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>2.44</v>
       </c>
       <c r="I2">
         <v>990</v>
       </c>
       <c r="J2">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1087,13 +1105,13 @@
         <v>1.1</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
         <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="R2">
         <v>1.13</v>
@@ -1111,7 +1129,7 @@
         <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1282,7 +1300,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1290,73 +1308,73 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F3">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="G3">
+        <v>2.12</v>
+      </c>
+      <c r="H3">
         <v>4.6</v>
       </c>
-      <c r="H3">
-        <v>4.2</v>
-      </c>
       <c r="I3">
-        <v>990</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1.32</v>
+        <v>2.76</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O3">
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
         <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1413,55 +1431,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1524,7 +1542,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1532,518 +1550,518 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
-        <v>16.5</v>
+        <v>2.66</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J4">
+        <v>3.45</v>
+      </c>
+      <c r="K4">
+        <v>3.95</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>3.6</v>
+      </c>
+      <c r="O4">
+        <v>1.2</v>
+      </c>
+      <c r="P4">
+        <v>2.06</v>
+      </c>
+      <c r="Q4">
+        <v>1.75</v>
+      </c>
+      <c r="R4">
+        <v>1.36</v>
+      </c>
+      <c r="S4">
+        <v>2.74</v>
+      </c>
+      <c r="T4">
         <v>1.11</v>
       </c>
-      <c r="K4">
-        <v>3.7</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>1.38</v>
-      </c>
-      <c r="Q4">
+      <c r="U4">
+        <v>1.11</v>
+      </c>
+      <c r="V4">
+        <v>1.43</v>
+      </c>
+      <c r="W4">
+        <v>1.6</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
         <v>1.01</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F5">
-        <v>1.71</v>
+        <v>5.9</v>
       </c>
       <c r="G5">
-        <v>1.83</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>1.38</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>1.54</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
+        <v>1.17</v>
+      </c>
+      <c r="R5">
+        <v>1.51</v>
+      </c>
+      <c r="S5">
+        <v>2.08</v>
+      </c>
+      <c r="T5">
+        <v>1.11</v>
+      </c>
+      <c r="U5">
+        <v>1.11</v>
+      </c>
+      <c r="V5">
+        <v>2.84</v>
+      </c>
+      <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
         <v>1.01</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F6">
-        <v>1.05</v>
+        <v>2.56</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="H6">
-        <v>1.99</v>
+        <v>3.05</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2058,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2250,42 +2268,42 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
         <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2300,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2492,42 +2510,42 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
         <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F8">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="H8">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="I8">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2542,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2734,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2742,64 +2760,64 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
         <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F9">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>2.26</v>
+        <v>600</v>
       </c>
       <c r="H9">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>3.65</v>
+        <v>870</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>1.06</v>
       </c>
       <c r="K9">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2808,210 +2826,210 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BG9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F10">
-        <v>1.09</v>
+        <v>5.6</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>1.57</v>
       </c>
       <c r="J10">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3026,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3218,42 +3236,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="G11">
-        <v>600</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
-        <v>1.08</v>
+        <v>2.46</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>2.84</v>
       </c>
       <c r="J11">
-        <v>1.09</v>
+        <v>2.78</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3271,7 +3289,7 @@
         <v>1.43</v>
       </c>
       <c r="Q11">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3460,42 +3478,42 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12">
-        <v>6.4</v>
+        <v>1.53</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="J12">
-        <v>1.06</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3510,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3702,290 +3720,290 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F13">
+        <v>2.22</v>
+      </c>
+      <c r="G13">
+        <v>2.24</v>
+      </c>
+      <c r="H13">
+        <v>3.55</v>
+      </c>
+      <c r="I13">
+        <v>3.65</v>
+      </c>
+      <c r="J13">
+        <v>3.6</v>
+      </c>
+      <c r="K13">
+        <v>3.7</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>4.2</v>
+      </c>
+      <c r="O13">
+        <v>1.28</v>
+      </c>
+      <c r="P13">
+        <v>2.12</v>
+      </c>
+      <c r="Q13">
+        <v>1.84</v>
+      </c>
+      <c r="R13">
+        <v>1.42</v>
+      </c>
+      <c r="S13">
+        <v>3.15</v>
+      </c>
+      <c r="T13">
+        <v>1.68</v>
+      </c>
+      <c r="U13">
+        <v>2.36</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>16.5</v>
+      </c>
+      <c r="Y13">
+        <v>16</v>
+      </c>
+      <c r="Z13">
+        <v>28</v>
+      </c>
+      <c r="AA13">
+        <v>75</v>
+      </c>
+      <c r="AB13">
+        <v>11.5</v>
+      </c>
+      <c r="AC13">
+        <v>8.6</v>
+      </c>
+      <c r="AD13">
+        <v>14.5</v>
+      </c>
+      <c r="AE13">
+        <v>46</v>
+      </c>
+      <c r="AF13">
+        <v>16</v>
+      </c>
+      <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>16</v>
+      </c>
+      <c r="AI13">
+        <v>46</v>
+      </c>
+      <c r="AJ13">
+        <v>36</v>
+      </c>
+      <c r="AK13">
+        <v>23</v>
+      </c>
+      <c r="AL13">
+        <v>36</v>
+      </c>
+      <c r="AM13">
+        <v>90</v>
+      </c>
+      <c r="AN13">
+        <v>16.5</v>
+      </c>
+      <c r="AO13">
+        <v>36</v>
+      </c>
+      <c r="AP13">
+        <v>15</v>
+      </c>
+      <c r="AQ13">
+        <v>13.5</v>
+      </c>
+      <c r="AR13">
+        <v>18</v>
+      </c>
+      <c r="AS13">
+        <v>30</v>
+      </c>
+      <c r="AT13">
+        <v>10</v>
+      </c>
+      <c r="AU13">
         <v>7.4</v>
       </c>
-      <c r="G13">
-        <v>1000</v>
-      </c>
-      <c r="H13">
-        <v>1.04</v>
-      </c>
-      <c r="I13">
-        <v>1.4</v>
-      </c>
-      <c r="J13">
-        <v>1.11</v>
-      </c>
-      <c r="K13">
-        <v>1000</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>2.7</v>
-      </c>
-      <c r="Q13">
-        <v>1.01</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>1.11</v>
-      </c>
-      <c r="U13">
-        <v>1.11</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13">
-        <v>1.01</v>
-      </c>
-      <c r="AR13">
-        <v>1.01</v>
-      </c>
-      <c r="AS13">
-        <v>1.01</v>
-      </c>
-      <c r="AT13">
-        <v>1.01</v>
-      </c>
-      <c r="AU13">
-        <v>1.01</v>
-      </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F14">
-        <v>1.99</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2.62</v>
+        <v>14.5</v>
       </c>
       <c r="H14">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="I14">
-        <v>3.8</v>
+        <v>1.36</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3994,10 +4012,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.12</v>
+        <v>2.74</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4006,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4018,112 +4036,112 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Y14">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="Z14">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AA14">
-        <v>65</v>
+        <v>13.5</v>
       </c>
       <c r="AB14">
+        <v>55</v>
+      </c>
+      <c r="AC14">
+        <v>18.5</v>
+      </c>
+      <c r="AD14">
+        <v>13.5</v>
+      </c>
+      <c r="AE14">
         <v>17</v>
       </c>
-      <c r="AC14">
-        <v>12</v>
-      </c>
-      <c r="AD14">
-        <v>17.5</v>
-      </c>
-      <c r="AE14">
+      <c r="AF14">
+        <v>130</v>
+      </c>
+      <c r="AG14">
+        <v>48</v>
+      </c>
+      <c r="AH14">
+        <v>34</v>
+      </c>
+      <c r="AI14">
         <v>40</v>
       </c>
-      <c r="AF14">
-        <v>21</v>
-      </c>
-      <c r="AG14">
-        <v>14</v>
-      </c>
-      <c r="AH14">
-        <v>18.5</v>
-      </c>
-      <c r="AI14">
-        <v>44</v>
-      </c>
       <c r="AJ14">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="AK14">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AM14">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AN14">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="AO14">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="AP14">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="AQ14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR14">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AT14">
+        <v>4.1</v>
+      </c>
+      <c r="AU14">
+        <v>12.5</v>
+      </c>
+      <c r="AV14">
+        <v>9.6</v>
+      </c>
+      <c r="AW14">
         <v>10</v>
       </c>
-      <c r="AU14">
-        <v>7.2</v>
-      </c>
-      <c r="AV14">
-        <v>10.5</v>
-      </c>
-      <c r="AW14">
-        <v>1.03</v>
-      </c>
       <c r="AX14">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY14">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="AZ14">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB14">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BC14">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BD14">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF14">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG14">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4186,42 +4204,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G15">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="H15">
-        <v>1.34</v>
+        <v>8.4</v>
       </c>
       <c r="I15">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="J15">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4236,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4428,43 +4446,43 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F16">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="G16">
+        <v>2.92</v>
+      </c>
+      <c r="H16">
+        <v>2.78</v>
+      </c>
+      <c r="I16">
+        <v>3.8</v>
+      </c>
+      <c r="J16">
+        <v>3.25</v>
+      </c>
+      <c r="K16">
         <v>3.9</v>
       </c>
-      <c r="H16">
-        <v>1.36</v>
-      </c>
-      <c r="I16">
-        <v>2.24</v>
-      </c>
-      <c r="J16">
-        <v>3.35</v>
-      </c>
-      <c r="K16">
-        <v>950</v>
-      </c>
       <c r="L16">
         <v>0</v>
       </c>
@@ -4478,10 +4496,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="Q16">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4670,60 +4688,60 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F17">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="G17">
-        <v>3.65</v>
+        <v>1.92</v>
       </c>
       <c r="H17">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>3.95</v>
+      </c>
+      <c r="K17">
+        <v>4.6</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
         <v>2.32</v>
       </c>
-      <c r="J17">
-        <v>3.85</v>
-      </c>
-      <c r="K17">
-        <v>4.5</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>2.38</v>
-      </c>
       <c r="Q17">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4912,42 +4930,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="G18">
-        <v>600</v>
+        <v>2.04</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I18">
-        <v>870</v>
+        <v>5.3</v>
       </c>
       <c r="J18">
-        <v>1.06</v>
+        <v>3.6</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4962,10 +4980,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="Q18">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5154,42 +5172,42 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F19">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="G19">
-        <v>600</v>
+        <v>1.6</v>
       </c>
       <c r="H19">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>870</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>1.51</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5204,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5396,39 +5414,39 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F20">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="G20">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H20">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="I20">
-        <v>60</v>
+        <v>5.1</v>
       </c>
       <c r="J20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
         <v>3.75</v>
@@ -5446,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="Q20">
         <v>2.14</v>
@@ -5638,42 +5656,42 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F21">
-        <v>1.3</v>
+        <v>2.32</v>
       </c>
       <c r="G21">
-        <v>1.6</v>
+        <v>2.58</v>
       </c>
       <c r="H21">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J21">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5688,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5880,42 +5898,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F22">
-        <v>1.32</v>
+        <v>2.76</v>
       </c>
       <c r="G22">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="H22">
-        <v>3.65</v>
+        <v>2.24</v>
       </c>
       <c r="I22">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5930,10 +5948,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q22">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6122,42 +6140,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F23">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="G23">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="H23">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>2.32</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6172,10 +6190,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6364,42 +6382,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F24">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="G24">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="H24">
-        <v>2.98</v>
+        <v>2.04</v>
       </c>
       <c r="I24">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="J24">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6414,10 +6432,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6606,72 +6624,72 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F25">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="G25">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H25">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I25">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="J25">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q25">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="R25">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -6680,175 +6698,175 @@
         <v>0</v>
       </c>
       <c r="X25">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AL25">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO25">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR25">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AS25">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU25">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW25">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AX25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AY25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ25">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BB25">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BC25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BD25">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BE25">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BF25">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BG25">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6856,241 +6874,725 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
         <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F26">
+        <v>2.1</v>
+      </c>
+      <c r="G26">
+        <v>2.38</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>3.8</v>
+      </c>
+      <c r="J26">
+        <v>3.75</v>
+      </c>
+      <c r="K26">
+        <v>4.5</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>2.36</v>
+      </c>
+      <c r="Q26">
+        <v>1.58</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>28</v>
+      </c>
+      <c r="Y26">
+        <v>22</v>
+      </c>
+      <c r="Z26">
+        <v>28</v>
+      </c>
+      <c r="AA26">
+        <v>65</v>
+      </c>
+      <c r="AB26">
+        <v>15</v>
+      </c>
+      <c r="AC26">
+        <v>10.5</v>
+      </c>
+      <c r="AD26">
+        <v>17.5</v>
+      </c>
+      <c r="AE26">
+        <v>40</v>
+      </c>
+      <c r="AF26">
+        <v>21</v>
+      </c>
+      <c r="AG26">
+        <v>14</v>
+      </c>
+      <c r="AH26">
+        <v>18.5</v>
+      </c>
+      <c r="AI26">
+        <v>44</v>
+      </c>
+      <c r="AJ26">
+        <v>36</v>
+      </c>
+      <c r="AK26">
+        <v>26</v>
+      </c>
+      <c r="AL26">
+        <v>36</v>
+      </c>
+      <c r="AM26">
+        <v>65</v>
+      </c>
+      <c r="AN26">
+        <v>14</v>
+      </c>
+      <c r="AO26">
+        <v>27</v>
+      </c>
+      <c r="AP26">
+        <v>16.5</v>
+      </c>
+      <c r="AQ26">
+        <v>15</v>
+      </c>
+      <c r="AR26">
+        <v>4.1</v>
+      </c>
+      <c r="AS26">
+        <v>4.4</v>
+      </c>
+      <c r="AT26">
+        <v>11.5</v>
+      </c>
+      <c r="AU26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV26">
+        <v>12</v>
+      </c>
+      <c r="AW26">
+        <v>23</v>
+      </c>
+      <c r="AX26">
+        <v>12.5</v>
+      </c>
+      <c r="AY26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ26">
+        <v>11</v>
+      </c>
+      <c r="BA26">
+        <v>25</v>
+      </c>
+      <c r="BB26">
+        <v>4.2</v>
+      </c>
+      <c r="BC26">
+        <v>15</v>
+      </c>
+      <c r="BD26">
+        <v>20</v>
+      </c>
+      <c r="BE26">
+        <v>4.4</v>
+      </c>
+      <c r="BF26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG26">
+        <v>18.5</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27">
+        <v>3.25</v>
+      </c>
+      <c r="G27">
+        <v>3.3</v>
+      </c>
+      <c r="H27">
+        <v>2.36</v>
+      </c>
+      <c r="I27">
+        <v>2.4</v>
+      </c>
+      <c r="J27">
+        <v>3.6</v>
+      </c>
+      <c r="K27">
+        <v>3.7</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.06</v>
+      </c>
+      <c r="N27">
+        <v>4.1</v>
+      </c>
+      <c r="O27">
+        <v>1.29</v>
+      </c>
+      <c r="P27">
+        <v>2.1</v>
+      </c>
+      <c r="Q27">
+        <v>1.85</v>
+      </c>
+      <c r="R27">
+        <v>1.41</v>
+      </c>
+      <c r="S27">
+        <v>3.15</v>
+      </c>
+      <c r="T27">
+        <v>1.7</v>
+      </c>
+      <c r="U27">
+        <v>2.34</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>16.5</v>
+      </c>
+      <c r="Y27">
+        <v>11.5</v>
+      </c>
+      <c r="Z27">
+        <v>16</v>
+      </c>
+      <c r="AA27">
+        <v>34</v>
+      </c>
+      <c r="AB27">
+        <v>14</v>
+      </c>
+      <c r="AC27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>11</v>
+      </c>
+      <c r="AE27">
+        <v>24</v>
+      </c>
+      <c r="AF27">
+        <v>24</v>
+      </c>
+      <c r="AG27">
+        <v>14</v>
+      </c>
+      <c r="AH27">
+        <v>16.5</v>
+      </c>
+      <c r="AI27">
+        <v>38</v>
+      </c>
+      <c r="AJ27">
+        <v>60</v>
+      </c>
+      <c r="AK27">
+        <v>38</v>
+      </c>
+      <c r="AL27">
+        <v>46</v>
+      </c>
+      <c r="AM27">
+        <v>85</v>
+      </c>
+      <c r="AN27">
+        <v>32</v>
+      </c>
+      <c r="AO27">
+        <v>18</v>
+      </c>
+      <c r="AP27">
+        <v>15</v>
+      </c>
+      <c r="AQ27">
+        <v>10.5</v>
+      </c>
+      <c r="AR27">
+        <v>13.5</v>
+      </c>
+      <c r="AS27">
+        <v>21</v>
+      </c>
+      <c r="AT27">
+        <v>12</v>
+      </c>
+      <c r="AU27">
+        <v>7.4</v>
+      </c>
+      <c r="AV27">
+        <v>10</v>
+      </c>
+      <c r="AW27">
+        <v>20</v>
+      </c>
+      <c r="AX27">
+        <v>20</v>
+      </c>
+      <c r="AY27">
+        <v>12</v>
+      </c>
+      <c r="AZ27">
+        <v>14.5</v>
+      </c>
+      <c r="BA27">
+        <v>22</v>
+      </c>
+      <c r="BB27">
+        <v>28</v>
+      </c>
+      <c r="BC27">
+        <v>22</v>
+      </c>
+      <c r="BD27">
+        <v>25</v>
+      </c>
+      <c r="BE27">
+        <v>46</v>
+      </c>
+      <c r="BF27">
+        <v>19.5</v>
+      </c>
+      <c r="BG27">
+        <v>15</v>
+      </c>
+      <c r="BH27">
+        <v>4.2</v>
+      </c>
+      <c r="BI27">
+        <v>2.84</v>
+      </c>
+      <c r="BJ27">
+        <v>11.5</v>
+      </c>
+      <c r="BK27">
+        <v>3.3</v>
+      </c>
+      <c r="BL27">
+        <v>130</v>
+      </c>
+      <c r="BM27">
+        <v>4.4</v>
+      </c>
+      <c r="BN27">
+        <v>7.8</v>
+      </c>
+      <c r="BO27">
+        <v>4.9</v>
+      </c>
+      <c r="BP27">
+        <v>30</v>
+      </c>
+      <c r="BQ27">
+        <v>4</v>
+      </c>
+      <c r="BR27">
+        <v>42</v>
+      </c>
+      <c r="BS27">
+        <v>4.1</v>
+      </c>
+      <c r="BT27">
+        <v>6.4</v>
+      </c>
+      <c r="BU27">
+        <v>4.1</v>
+      </c>
+      <c r="BV27">
+        <v>21</v>
+      </c>
+      <c r="BW27">
+        <v>3.75</v>
+      </c>
+      <c r="BX27">
+        <v>36</v>
+      </c>
+      <c r="BY27">
+        <v>4.1</v>
+      </c>
+      <c r="BZ27">
+        <v>29</v>
+      </c>
+      <c r="CA27">
+        <v>3.95</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28">
         <v>1.04</v>
       </c>
-      <c r="G26">
-        <v>1000</v>
-      </c>
-      <c r="H26">
+      <c r="G28">
+        <v>600</v>
+      </c>
+      <c r="H28">
         <v>1.04</v>
       </c>
-      <c r="I26">
-        <v>1000</v>
-      </c>
-      <c r="J26">
-        <v>1.04</v>
-      </c>
-      <c r="K26">
+      <c r="I28">
+        <v>870</v>
+      </c>
+      <c r="J28">
+        <v>1.06</v>
+      </c>
+      <c r="K28">
         <v>950</v>
       </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
         <v>1.24</v>
       </c>
-      <c r="Q26">
+      <c r="Q28">
         <v>1.01</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AO26">
-        <v>0</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>0</v>
-      </c>
-      <c r="BC26">
-        <v>0</v>
-      </c>
-      <c r="BD26">
-        <v>0</v>
-      </c>
-      <c r="BE26">
-        <v>0</v>
-      </c>
-      <c r="BF26">
-        <v>0</v>
-      </c>
-      <c r="BG26">
-        <v>0</v>
-      </c>
-      <c r="BH26">
-        <v>0</v>
-      </c>
-      <c r="BI26">
-        <v>0</v>
-      </c>
-      <c r="BJ26">
-        <v>0</v>
-      </c>
-      <c r="BK26">
-        <v>0</v>
-      </c>
-      <c r="BL26">
-        <v>0</v>
-      </c>
-      <c r="BM26">
-        <v>0</v>
-      </c>
-      <c r="BN26">
-        <v>0</v>
-      </c>
-      <c r="BO26">
-        <v>0</v>
-      </c>
-      <c r="BP26">
-        <v>0</v>
-      </c>
-      <c r="BQ26">
-        <v>0</v>
-      </c>
-      <c r="BR26">
-        <v>0</v>
-      </c>
-      <c r="BS26">
-        <v>0</v>
-      </c>
-      <c r="BT26">
-        <v>0</v>
-      </c>
-      <c r="BU26">
-        <v>0</v>
-      </c>
-      <c r="BV26">
-        <v>0</v>
-      </c>
-      <c r="BW26">
-        <v>0</v>
-      </c>
-      <c r="BX26">
-        <v>0</v>
-      </c>
-      <c r="BY26">
-        <v>0</v>
-      </c>
-      <c r="BZ26">
-        <v>0</v>
-      </c>
-      <c r="CA26">
-        <v>0</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>150</v>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="170">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,12 @@
     <t>South Korean K2 League</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
@@ -292,6 +298,15 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -334,6 +349,18 @@
     <t>Ansan Greeners FC</t>
   </si>
   <si>
+    <t>Dalian Yingbo</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Shenzhen Peng City</t>
+  </si>
+  <si>
+    <t>Kolos Kovalyovka</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
@@ -349,21 +376,21 @@
     <t>Qatar SC</t>
   </si>
   <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
+    <t>Racing Santander</t>
+  </si>
+  <si>
     <t>Al Ittihad (EGY)</t>
   </si>
   <si>
-    <t>ZED FC</t>
-  </si>
-  <si>
-    <t>Racing Santander</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Altrincham</t>
   </si>
   <si>
@@ -415,6 +442,18 @@
     <t>Daegu Fc</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
+    <t>Shandong Taishan</t>
+  </si>
+  <si>
+    <t>Shanghai Port FC</t>
+  </si>
+  <si>
+    <t>Obolon-Brovar Kiev</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
@@ -430,21 +469,21 @@
     <t>Al-Sadd</t>
   </si>
   <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Elche</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Al Ahly Cairo</t>
-  </si>
-  <si>
-    <t>Elche</t>
+    <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
     <t>Al-Hilal</t>
   </si>
   <si>
-    <t>Al-Taawoun Buraidah</t>
-  </si>
-  <si>
     <t>FC Halifax Town</t>
   </si>
   <si>
@@ -484,7 +523,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-08-26 08:13:39</t>
+    <t>2026-08-26 10:23:20</t>
   </si>
 </sst>
 </file>
@@ -816,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1066,16 +1105,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F2">
         <v>1.09</v>
@@ -1084,7 +1123,7 @@
         <v>990</v>
       </c>
       <c r="H2">
-        <v>2.44</v>
+        <v>1.09</v>
       </c>
       <c r="I2">
         <v>990</v>
@@ -1129,7 +1168,7 @@
         <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1300,7 +1339,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1308,40 +1347,40 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F3">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="H3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>2.76</v>
+        <v>2.26</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
         <v>2.54</v>
@@ -1353,28 +1392,28 @@
         <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="X3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1431,55 +1470,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1542,7 +1581,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1550,58 +1589,58 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F4">
         <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H4">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="P4">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
         <v>1.36</v>
       </c>
       <c r="S4">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1610,10 +1649,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1784,7 +1823,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1792,58 +1831,58 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F5">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="G5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="I5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="J5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="Q5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1852,10 +1891,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2026,7 +2065,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2034,1002 +2073,1002 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="G6">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="H6">
-        <v>3.05</v>
+        <v>1.99</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>2.44</v>
       </c>
       <c r="J6">
-        <v>2.54</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F7">
         <v>1.71</v>
       </c>
       <c r="G7">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P7">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F8">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="I8">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
+        <v>1.14</v>
+      </c>
+      <c r="R8">
+        <v>1.64</v>
+      </c>
+      <c r="S8">
+        <v>2.2</v>
+      </c>
+      <c r="T8">
+        <v>1.45</v>
+      </c>
+      <c r="U8">
+        <v>2.66</v>
+      </c>
+      <c r="V8">
         <v>1.72</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>2.2</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="I9">
         <v>870</v>
       </c>
       <c r="J9">
-        <v>1.06</v>
+        <v>1.86</v>
       </c>
       <c r="K9">
         <v>950</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
         <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F10">
-        <v>5.6</v>
+        <v>2.56</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="H10">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="I10">
-        <v>1.57</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="K10">
-        <v>8.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3044,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>1.38</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3236,42 +3275,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F11">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>1.88</v>
       </c>
       <c r="H11">
-        <v>2.46</v>
+        <v>3.75</v>
       </c>
       <c r="I11">
-        <v>2.84</v>
+        <v>870</v>
       </c>
       <c r="J11">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
-        <v>3.1</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3286,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.43</v>
+        <v>2.42</v>
       </c>
       <c r="Q11">
-        <v>2.98</v>
+        <v>1.38</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3478,42 +3517,42 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F12">
-        <v>8.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="G12">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="H12">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="I12">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3528,10 +3567,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3720,72 +3759,72 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F13">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G13">
-        <v>2.24</v>
+        <v>600</v>
       </c>
       <c r="H13">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
-        <v>3.65</v>
+        <v>870</v>
       </c>
       <c r="J13">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3794,210 +3833,210 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY13">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BG13">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH13">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI13">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BJ13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK13">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BL13">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM13">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BN13">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO13">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP13">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS13">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BT13">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU13">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BV13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW13">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BX13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY13">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BZ13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="G14">
-        <v>14.5</v>
+        <v>600</v>
       </c>
       <c r="H14">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="I14">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="J14">
-        <v>5.9</v>
+        <v>2.76</v>
       </c>
       <c r="K14">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4012,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4024,10 +4063,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4036,112 +4075,112 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4204,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4212,34 +4251,34 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F15">
-        <v>1.34</v>
+        <v>6.6</v>
       </c>
       <c r="G15">
-        <v>1.43</v>
+        <v>13.5</v>
       </c>
       <c r="H15">
-        <v>8.4</v>
+        <v>1.53</v>
       </c>
       <c r="I15">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
       <c r="J15">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4254,10 +4293,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q15">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4446,72 +4485,72 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F16">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="H16">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="I16">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P16">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4520,210 +4559,210 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="F17">
-        <v>1.75</v>
+        <v>3.55</v>
       </c>
       <c r="G17">
-        <v>1.92</v>
+        <v>4.1</v>
       </c>
       <c r="H17">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>2.78</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="K17">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4738,10 +4777,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.32</v>
+        <v>1.37</v>
       </c>
       <c r="Q17">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4930,42 +4969,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F18">
-        <v>1.87</v>
+        <v>1.31</v>
       </c>
       <c r="G18">
-        <v>2.04</v>
+        <v>1.49</v>
       </c>
       <c r="H18">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J18">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>500</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4980,10 +5019,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5172,42 +5211,42 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F19">
-        <v>1.54</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G19">
-        <v>1.6</v>
+        <v>1000</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>1.39</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5222,10 +5261,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5234,10 +5273,10 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5246,112 +5285,112 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>0</v>
@@ -5414,42 +5453,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F20">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="G20">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>4.4</v>
+        <v>1.52</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K20">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5464,10 +5503,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.64</v>
+        <v>1.12</v>
       </c>
       <c r="Q20">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5656,42 +5695,42 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F21">
-        <v>2.32</v>
+        <v>1.63</v>
       </c>
       <c r="G21">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="H21">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5706,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5898,42 +5937,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F22">
-        <v>2.76</v>
+        <v>1.72</v>
       </c>
       <c r="G22">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="H22">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="I22">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5948,10 +5987,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="Q22">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6140,42 +6179,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F23">
-        <v>3.1</v>
+        <v>1.46</v>
       </c>
       <c r="G23">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="H23">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>2.32</v>
+        <v>870</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6190,10 +6229,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q23">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6382,42 +6421,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F24">
-        <v>3.45</v>
+        <v>1.74</v>
       </c>
       <c r="G24">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="H24">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="I24">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="J24">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6432,10 +6471,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.28</v>
+        <v>1.12</v>
       </c>
       <c r="Q24">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6624,42 +6663,42 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F25">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="G25">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="H25">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="I25">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K25">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6674,10 +6713,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.14</v>
+        <v>1.12</v>
       </c>
       <c r="Q25">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6866,48 +6905,48 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F26">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="G26">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="I26">
+        <v>2.58</v>
+      </c>
+      <c r="J26">
         <v>3.8</v>
       </c>
-      <c r="J26">
-        <v>3.75</v>
-      </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -6916,10 +6955,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -6940,112 +6979,112 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AO26">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR26">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AS26">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AT26">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU26">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV26">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW26">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY26">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BA26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BB26">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BG26">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BH26">
         <v>0</v>
@@ -7108,72 +7147,72 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F27">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="H27">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="I27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J27">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K27">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q27">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="R27">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7182,417 +7221,1385 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BG27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH27">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI27">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BJ27">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK27">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BL27">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM27">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BN27">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BO27">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BQ27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR27">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BT27">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BV27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW27">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BX27">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BZ27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CA27">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28">
+        <v>3.2</v>
+      </c>
+      <c r="G28">
+        <v>3.6</v>
+      </c>
+      <c r="H28">
+        <v>2.04</v>
+      </c>
+      <c r="I28">
+        <v>2.24</v>
+      </c>
+      <c r="J28">
+        <v>3.6</v>
+      </c>
+      <c r="K28">
+        <v>4.3</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>2.06</v>
+      </c>
+      <c r="Q28">
+        <v>1.56</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29">
+        <v>2.82</v>
+      </c>
+      <c r="G29">
+        <v>3.45</v>
+      </c>
+      <c r="H29">
+        <v>2.42</v>
+      </c>
+      <c r="I29">
+        <v>2.82</v>
+      </c>
+      <c r="J29">
+        <v>3.4</v>
+      </c>
+      <c r="K29">
+        <v>4.4</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>2.1</v>
+      </c>
+      <c r="Q29">
+        <v>1.7</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30">
+        <v>1.38</v>
+      </c>
+      <c r="G30">
+        <v>2.6</v>
+      </c>
+      <c r="H30">
+        <v>3.05</v>
+      </c>
+      <c r="I30">
+        <v>3.75</v>
+      </c>
+      <c r="J30">
+        <v>3.4</v>
+      </c>
+      <c r="K30">
+        <v>950</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.12</v>
+      </c>
+      <c r="Q30">
+        <v>1.01</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>1000</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>1000</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>1000</v>
+      </c>
+      <c r="AC30">
+        <v>1000</v>
+      </c>
+      <c r="AD30">
+        <v>1000</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>1000</v>
+      </c>
+      <c r="AG30">
+        <v>1000</v>
+      </c>
+      <c r="AH30">
+        <v>1000</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>1000</v>
+      </c>
+      <c r="AK30">
+        <v>1000</v>
+      </c>
+      <c r="AL30">
+        <v>1000</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>1000</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30">
+        <v>1.01</v>
+      </c>
+      <c r="AR30">
+        <v>1.01</v>
+      </c>
+      <c r="AS30">
+        <v>1.01</v>
+      </c>
+      <c r="AT30">
+        <v>1.01</v>
+      </c>
+      <c r="AU30">
+        <v>1.01</v>
+      </c>
+      <c r="AV30">
+        <v>1.01</v>
+      </c>
+      <c r="AW30">
+        <v>1.01</v>
+      </c>
+      <c r="AX30">
+        <v>1.01</v>
+      </c>
+      <c r="AY30">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30">
+        <v>1.01</v>
+      </c>
+      <c r="BA30">
+        <v>1.01</v>
+      </c>
+      <c r="BB30">
+        <v>1.01</v>
+      </c>
+      <c r="BC30">
+        <v>1.01</v>
+      </c>
+      <c r="BD30">
+        <v>1.01</v>
+      </c>
+      <c r="BE30">
+        <v>1.01</v>
+      </c>
+      <c r="BF30">
+        <v>1.01</v>
+      </c>
+      <c r="BG30">
+        <v>1.01</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
+        <v>0</v>
+      </c>
+      <c r="BQ30">
+        <v>0</v>
+      </c>
+      <c r="BR30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>0</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>0</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>0</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
         <v>88</v>
       </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28">
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31">
+        <v>3.2</v>
+      </c>
+      <c r="G31">
+        <v>3.3</v>
+      </c>
+      <c r="H31">
+        <v>2.38</v>
+      </c>
+      <c r="I31">
+        <v>2.4</v>
+      </c>
+      <c r="J31">
+        <v>3.6</v>
+      </c>
+      <c r="K31">
+        <v>3.7</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1.06</v>
+      </c>
+      <c r="N31">
+        <v>4.1</v>
+      </c>
+      <c r="O31">
+        <v>1.28</v>
+      </c>
+      <c r="P31">
+        <v>2.04</v>
+      </c>
+      <c r="Q31">
+        <v>1.86</v>
+      </c>
+      <c r="R31">
+        <v>1.39</v>
+      </c>
+      <c r="S31">
+        <v>3.25</v>
+      </c>
+      <c r="T31">
+        <v>1.67</v>
+      </c>
+      <c r="U31">
+        <v>2.3</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>16.5</v>
+      </c>
+      <c r="Y31">
+        <v>12</v>
+      </c>
+      <c r="Z31">
+        <v>16.5</v>
+      </c>
+      <c r="AA31">
+        <v>38</v>
+      </c>
+      <c r="AB31">
+        <v>14.5</v>
+      </c>
+      <c r="AC31">
+        <v>9.6</v>
+      </c>
+      <c r="AD31">
+        <v>11</v>
+      </c>
+      <c r="AE31">
+        <v>27</v>
+      </c>
+      <c r="AF31">
+        <v>26</v>
+      </c>
+      <c r="AG31">
+        <v>14.5</v>
+      </c>
+      <c r="AH31">
+        <v>20</v>
+      </c>
+      <c r="AI31">
+        <v>55</v>
+      </c>
+      <c r="AJ31">
+        <v>290</v>
+      </c>
+      <c r="AK31">
+        <v>75</v>
+      </c>
+      <c r="AL31">
+        <v>55</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>36</v>
+      </c>
+      <c r="AO31">
+        <v>19.5</v>
+      </c>
+      <c r="AP31">
+        <v>13.5</v>
+      </c>
+      <c r="AQ31">
+        <v>9.6</v>
+      </c>
+      <c r="AR31">
+        <v>12.5</v>
+      </c>
+      <c r="AS31">
+        <v>5.6</v>
+      </c>
+      <c r="AT31">
+        <v>11.5</v>
+      </c>
+      <c r="AU31">
+        <v>7.4</v>
+      </c>
+      <c r="AV31">
+        <v>10</v>
+      </c>
+      <c r="AW31">
+        <v>18</v>
+      </c>
+      <c r="AX31">
+        <v>19</v>
+      </c>
+      <c r="AY31">
+        <v>11</v>
+      </c>
+      <c r="AZ31">
+        <v>14.5</v>
+      </c>
+      <c r="BA31">
+        <v>5.9</v>
+      </c>
+      <c r="BB31">
+        <v>6.4</v>
+      </c>
+      <c r="BC31">
+        <v>5.9</v>
+      </c>
+      <c r="BD31">
+        <v>5.9</v>
+      </c>
+      <c r="BE31">
+        <v>29</v>
+      </c>
+      <c r="BF31">
+        <v>5.6</v>
+      </c>
+      <c r="BG31">
+        <v>14</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
         <v>1.04</v>
       </c>
-      <c r="G28">
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.04</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.04</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.04</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.04</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.04</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.04</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.04</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.04</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.04</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32">
+        <v>1.04</v>
+      </c>
+      <c r="G32">
         <v>600</v>
       </c>
-      <c r="H28">
+      <c r="H32">
         <v>1.04</v>
       </c>
-      <c r="I28">
+      <c r="I32">
         <v>870</v>
       </c>
-      <c r="J28">
-        <v>1.06</v>
-      </c>
-      <c r="K28">
+      <c r="J32">
+        <v>1.09</v>
+      </c>
+      <c r="K32">
         <v>950</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>1.24</v>
       </c>
-      <c r="Q28">
-        <v>1.01</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AO28">
-        <v>0</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>0</v>
-      </c>
-      <c r="BC28">
-        <v>0</v>
-      </c>
-      <c r="BD28">
-        <v>0</v>
-      </c>
-      <c r="BE28">
-        <v>0</v>
-      </c>
-      <c r="BF28">
-        <v>0</v>
-      </c>
-      <c r="BG28">
-        <v>0</v>
-      </c>
-      <c r="BH28">
-        <v>0</v>
-      </c>
-      <c r="BI28">
-        <v>0</v>
-      </c>
-      <c r="BJ28">
-        <v>0</v>
-      </c>
-      <c r="BK28">
-        <v>0</v>
-      </c>
-      <c r="BL28">
-        <v>0</v>
-      </c>
-      <c r="BM28">
-        <v>0</v>
-      </c>
-      <c r="BN28">
-        <v>0</v>
-      </c>
-      <c r="BO28">
-        <v>0</v>
-      </c>
-      <c r="BP28">
-        <v>0</v>
-      </c>
-      <c r="BQ28">
-        <v>0</v>
-      </c>
-      <c r="BR28">
-        <v>0</v>
-      </c>
-      <c r="BS28">
-        <v>0</v>
-      </c>
-      <c r="BT28">
-        <v>0</v>
-      </c>
-      <c r="BU28">
-        <v>0</v>
-      </c>
-      <c r="BV28">
-        <v>0</v>
-      </c>
-      <c r="BW28">
-        <v>0</v>
-      </c>
-      <c r="BX28">
-        <v>0</v>
-      </c>
-      <c r="BY28">
-        <v>0</v>
-      </c>
-      <c r="BZ28">
-        <v>0</v>
-      </c>
-      <c r="CA28">
-        <v>0</v>
-      </c>
-      <c r="CB28" t="s">
-        <v>156</v>
+      <c r="Q32">
+        <v>1.01</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="176">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
@@ -313,6 +316,9 @@
     <t>14:15:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>15:50:00</t>
   </si>
   <si>
@@ -367,6 +373,9 @@
     <t>Al Ahli (QAT)</t>
   </si>
   <si>
+    <t>FC Voluntari</t>
+  </si>
+  <si>
     <t>Al Riyadh SC</t>
   </si>
   <si>
@@ -385,12 +394,18 @@
     <t>Al Ittihad (EGY)</t>
   </si>
   <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
     <t>Al Nassr</t>
   </si>
   <si>
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
+    <t>Barrow</t>
+  </si>
+  <si>
     <t>Altrincham</t>
   </si>
   <si>
@@ -403,9 +418,6 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>Barrow</t>
-  </si>
-  <si>
     <t>Hornchurch</t>
   </si>
   <si>
@@ -460,6 +472,9 @@
     <t>Lusail</t>
   </si>
   <si>
+    <t>Otelul Galati</t>
+  </si>
+  <si>
     <t>NEOM Sports Club</t>
   </si>
   <si>
@@ -478,12 +493,18 @@
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
+    <t>ACS Petrolul 52</t>
+  </si>
+  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
     <t>Al-Hilal</t>
   </si>
   <si>
+    <t>Yeovil</t>
+  </si>
+  <si>
     <t>FC Halifax Town</t>
   </si>
   <si>
@@ -496,9 +517,6 @@
     <t>Kidderminster</t>
   </si>
   <si>
-    <t>Yeovil</t>
-  </si>
-  <si>
     <t>Woking</t>
   </si>
   <si>
@@ -523,7 +541,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-08-26 10:23:20</t>
+    <t>2026-08-26 12:32:50</t>
   </si>
 </sst>
 </file>
@@ -855,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1105,19 +1123,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F2">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="G2">
         <v>990</v>
@@ -1129,10 +1147,10 @@
         <v>990</v>
       </c>
       <c r="J2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1168,7 +1186,7 @@
         <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1339,7 +1357,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1347,241 +1365,241 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F3">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="G3">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T3">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="U3">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="V3">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1589,241 +1607,241 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F4">
         <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H4">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1831,241 +1849,241 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F5">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="I5">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="CB5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2073,241 +2091,241 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F6">
         <v>2.96</v>
       </c>
       <c r="G6">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="H6">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="I6">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="O6">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
         <v>1.44</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="S6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W6">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2315,241 +2333,241 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G7">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H7">
         <v>4.1</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="K7">
         <v>5.5</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="O7">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P7">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q7">
         <v>1.29</v>
       </c>
       <c r="R7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>3.2</v>
       </c>
       <c r="V7">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2557,241 +2575,241 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H8">
         <v>2.2</v>
       </c>
       <c r="I8">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S8">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T8">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U8">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="W8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2799,175 +2817,175 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F9">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="H9">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
+        <v>1.44</v>
+      </c>
+      <c r="M9">
+        <v>1.11</v>
+      </c>
+      <c r="N9">
+        <v>2.6</v>
+      </c>
+      <c r="O9">
+        <v>1.53</v>
+      </c>
+      <c r="P9">
+        <v>1.54</v>
+      </c>
+      <c r="Q9">
+        <v>2.62</v>
+      </c>
+      <c r="R9">
+        <v>1.19</v>
+      </c>
+      <c r="S9">
+        <v>4.9</v>
+      </c>
+      <c r="T9">
+        <v>2.34</v>
+      </c>
+      <c r="U9">
+        <v>1.63</v>
+      </c>
+      <c r="V9">
+        <v>1.15</v>
+      </c>
+      <c r="W9">
+        <v>2.16</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>17.5</v>
+      </c>
+      <c r="Z9">
+        <v>65</v>
+      </c>
+      <c r="AA9">
+        <v>290</v>
+      </c>
+      <c r="AB9">
+        <v>6.8</v>
+      </c>
+      <c r="AC9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9">
+        <v>32</v>
+      </c>
+      <c r="AE9">
+        <v>170</v>
+      </c>
+      <c r="AF9">
+        <v>9.6</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>32</v>
+      </c>
+      <c r="AI9">
+        <v>190</v>
+      </c>
+      <c r="AJ9">
+        <v>21</v>
+      </c>
+      <c r="AK9">
+        <v>29</v>
+      </c>
+      <c r="AL9">
+        <v>75</v>
+      </c>
+      <c r="AM9">
+        <v>310</v>
+      </c>
+      <c r="AN9">
+        <v>21</v>
+      </c>
+      <c r="AO9">
+        <v>330</v>
+      </c>
+      <c r="AP9">
+        <v>7</v>
+      </c>
+      <c r="AQ9">
+        <v>12</v>
+      </c>
+      <c r="AR9">
+        <v>42</v>
+      </c>
+      <c r="AS9">
         <v>1.01</v>
       </c>
-      <c r="M9">
-        <v>1.01</v>
-      </c>
-      <c r="N9">
-        <v>2.98</v>
-      </c>
-      <c r="O9">
-        <v>1.01</v>
-      </c>
-      <c r="P9">
-        <v>1.24</v>
-      </c>
-      <c r="Q9">
-        <v>1.02</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
-      <c r="S9">
-        <v>1.45</v>
-      </c>
-      <c r="T9">
-        <v>1.01</v>
-      </c>
-      <c r="U9">
-        <v>1.01</v>
-      </c>
-      <c r="V9">
-        <v>1.01</v>
-      </c>
-      <c r="W9">
-        <v>1.83</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>1000</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>1000</v>
-      </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9">
-        <v>1.03</v>
-      </c>
-      <c r="AR9">
-        <v>1.03</v>
-      </c>
-      <c r="AS9">
-        <v>1.03</v>
-      </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
         <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9">
         <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG9">
         <v>1.01</v>
@@ -3033,7 +3051,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3041,241 +3059,241 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F10">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G10">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="H10">
+        <v>3.2</v>
+      </c>
+      <c r="I10">
+        <v>3.55</v>
+      </c>
+      <c r="J10">
+        <v>2.86</v>
+      </c>
+      <c r="K10">
         <v>3.15</v>
       </c>
-      <c r="I10">
-        <v>4.3</v>
-      </c>
-      <c r="J10">
-        <v>2.54</v>
-      </c>
-      <c r="K10">
-        <v>3.45</v>
-      </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P10">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3283,241 +3301,241 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F11">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G11">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H11">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>4.9</v>
       </c>
       <c r="J11">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="Q11">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3525,232 +3543,232 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F12">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="G12">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="H12">
-        <v>1.99</v>
+        <v>2.96</v>
       </c>
       <c r="I12">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="J12">
+        <v>3.2</v>
+      </c>
+      <c r="K12">
         <v>3.6</v>
       </c>
-      <c r="K12">
-        <v>4.9</v>
-      </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3759,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3767,34 +3785,34 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="G13">
-        <v>600</v>
+        <v>4.3</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="I13">
-        <v>870</v>
+        <v>2.24</v>
       </c>
       <c r="J13">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3809,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4001,39 +4019,39 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F14">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
         <v>600</v>
       </c>
       <c r="H14">
+        <v>1.04</v>
+      </c>
+      <c r="I14">
+        <v>870</v>
+      </c>
+      <c r="J14">
         <v>1.09</v>
-      </c>
-      <c r="I14">
-        <v>1.57</v>
-      </c>
-      <c r="J14">
-        <v>2.76</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4051,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q14">
         <v>1.01</v>
@@ -4243,42 +4261,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F15">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="H15">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="I15">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="J15">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4293,10 +4311,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4485,72 +4503,72 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G16">
-        <v>2.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="I16">
-        <v>3.6</v>
+        <v>1.56</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q16">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4559,452 +4577,452 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG16">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F17">
-        <v>3.55</v>
+        <v>2.24</v>
       </c>
       <c r="G17">
+        <v>2.26</v>
+      </c>
+      <c r="H17">
+        <v>3.5</v>
+      </c>
+      <c r="I17">
+        <v>3.6</v>
+      </c>
+      <c r="J17">
+        <v>3.6</v>
+      </c>
+      <c r="K17">
+        <v>3.65</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1.06</v>
+      </c>
+      <c r="N17">
+        <v>4.2</v>
+      </c>
+      <c r="O17">
+        <v>1.28</v>
+      </c>
+      <c r="P17">
+        <v>2.1</v>
+      </c>
+      <c r="Q17">
+        <v>1.84</v>
+      </c>
+      <c r="R17">
+        <v>1.42</v>
+      </c>
+      <c r="S17">
+        <v>3.1</v>
+      </c>
+      <c r="T17">
+        <v>1.68</v>
+      </c>
+      <c r="U17">
+        <v>2.36</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>16.5</v>
+      </c>
+      <c r="Y17">
+        <v>15</v>
+      </c>
+      <c r="Z17">
+        <v>28</v>
+      </c>
+      <c r="AA17">
+        <v>75</v>
+      </c>
+      <c r="AB17">
+        <v>11.5</v>
+      </c>
+      <c r="AC17">
+        <v>9.6</v>
+      </c>
+      <c r="AD17">
+        <v>14.5</v>
+      </c>
+      <c r="AE17">
+        <v>42</v>
+      </c>
+      <c r="AF17">
+        <v>16</v>
+      </c>
+      <c r="AG17">
+        <v>11</v>
+      </c>
+      <c r="AH17">
+        <v>16.5</v>
+      </c>
+      <c r="AI17">
+        <v>55</v>
+      </c>
+      <c r="AJ17">
+        <v>36</v>
+      </c>
+      <c r="AK17">
+        <v>24</v>
+      </c>
+      <c r="AL17">
+        <v>36</v>
+      </c>
+      <c r="AM17">
+        <v>90</v>
+      </c>
+      <c r="AN17">
+        <v>16.5</v>
+      </c>
+      <c r="AO17">
+        <v>40</v>
+      </c>
+      <c r="AP17">
+        <v>15</v>
+      </c>
+      <c r="AQ17">
+        <v>13.5</v>
+      </c>
+      <c r="AR17">
+        <v>18</v>
+      </c>
+      <c r="AS17">
+        <v>30</v>
+      </c>
+      <c r="AT17">
+        <v>10</v>
+      </c>
+      <c r="AU17">
+        <v>7.2</v>
+      </c>
+      <c r="AV17">
+        <v>12.5</v>
+      </c>
+      <c r="AW17">
+        <v>24</v>
+      </c>
+      <c r="AX17">
+        <v>13.5</v>
+      </c>
+      <c r="AY17">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>26</v>
+      </c>
+      <c r="BB17">
+        <v>19</v>
+      </c>
+      <c r="BC17">
+        <v>20</v>
+      </c>
+      <c r="BD17">
+        <v>21</v>
+      </c>
+      <c r="BE17">
+        <v>29</v>
+      </c>
+      <c r="BF17">
+        <v>14</v>
+      </c>
+      <c r="BG17">
+        <v>21</v>
+      </c>
+      <c r="BH17">
         <v>4.1</v>
       </c>
-      <c r="H17">
-        <v>2.44</v>
-      </c>
-      <c r="I17">
-        <v>2.78</v>
-      </c>
-      <c r="J17">
-        <v>2.7</v>
-      </c>
-      <c r="K17">
-        <v>3.25</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>1.37</v>
-      </c>
-      <c r="Q17">
-        <v>1.01</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>0</v>
-      </c>
-      <c r="BC17">
-        <v>0</v>
-      </c>
-      <c r="BD17">
-        <v>0</v>
-      </c>
-      <c r="BE17">
-        <v>0</v>
-      </c>
-      <c r="BF17">
-        <v>0</v>
-      </c>
-      <c r="BG17">
-        <v>0</v>
-      </c>
-      <c r="BH17">
-        <v>0</v>
-      </c>
       <c r="BI17">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F18">
-        <v>1.31</v>
+        <v>3.5</v>
       </c>
       <c r="G18">
-        <v>1.49</v>
+        <v>3.95</v>
       </c>
       <c r="H18">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="K18">
-        <v>500</v>
+        <v>3.05</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5019,10 +5037,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5211,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5219,34 +5237,34 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F19">
-        <v>8.199999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>1.9</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I19">
-        <v>1.39</v>
+        <v>6.6</v>
       </c>
       <c r="J19">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="K19">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5261,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q19">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5273,10 +5291,10 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5285,112 +5303,112 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH19">
         <v>0</v>
@@ -5453,42 +5471,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F20">
-        <v>2.38</v>
+        <v>1.32</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="H20">
-        <v>1.52</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20">
-        <v>3.85</v>
+        <v>12</v>
       </c>
       <c r="J20">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5503,10 +5521,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.12</v>
+        <v>2.78</v>
       </c>
       <c r="Q20">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5695,186 +5713,186 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F21">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>2.06</v>
+        <v>14.5</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>1.28</v>
       </c>
       <c r="I21">
+        <v>1.34</v>
+      </c>
+      <c r="J21">
+        <v>6.2</v>
+      </c>
+      <c r="K21">
+        <v>8</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.82</v>
+      </c>
+      <c r="Q21">
+        <v>1.41</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1.88</v>
+      </c>
+      <c r="U21">
+        <v>1.94</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>40</v>
+      </c>
+      <c r="Y21">
+        <v>14.5</v>
+      </c>
+      <c r="Z21">
+        <v>11.5</v>
+      </c>
+      <c r="AA21">
+        <v>13</v>
+      </c>
+      <c r="AB21">
+        <v>55</v>
+      </c>
+      <c r="AC21">
+        <v>18.5</v>
+      </c>
+      <c r="AD21">
+        <v>13.5</v>
+      </c>
+      <c r="AE21">
+        <v>17</v>
+      </c>
+      <c r="AF21">
+        <v>140</v>
+      </c>
+      <c r="AG21">
+        <v>50</v>
+      </c>
+      <c r="AH21">
+        <v>34</v>
+      </c>
+      <c r="AI21">
+        <v>36</v>
+      </c>
+      <c r="AJ21">
+        <v>460</v>
+      </c>
+      <c r="AK21">
+        <v>190</v>
+      </c>
+      <c r="AL21">
+        <v>140</v>
+      </c>
+      <c r="AM21">
+        <v>150</v>
+      </c>
+      <c r="AN21">
+        <v>210</v>
+      </c>
+      <c r="AO21">
+        <v>4.6</v>
+      </c>
+      <c r="AP21">
+        <v>23</v>
+      </c>
+      <c r="AQ21">
+        <v>10</v>
+      </c>
+      <c r="AR21">
         <v>8.199999999999999</v>
       </c>
-      <c r="J21">
-        <v>3.8</v>
-      </c>
-      <c r="K21">
-        <v>7.4</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>2.08</v>
-      </c>
-      <c r="Q21">
-        <v>1.51</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
       <c r="AS21">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BH21">
         <v>0</v>
@@ -5937,42 +5955,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F22">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="G22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H22">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="I22">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5987,10 +6005,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6179,42 +6197,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F23">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="G23">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>3.45</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="K23">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6229,10 +6247,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6421,42 +6439,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F24">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G24">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="H24">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I24">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K24">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6471,10 +6489,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6663,42 +6681,42 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F25">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="G25">
-        <v>2.88</v>
+        <v>2.04</v>
       </c>
       <c r="H25">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="I25">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J25">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K25">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6713,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6905,42 +6923,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F26">
-        <v>2.74</v>
+        <v>1.54</v>
       </c>
       <c r="G26">
-        <v>3.35</v>
+        <v>1.6</v>
       </c>
       <c r="H26">
-        <v>2.24</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>2.58</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K26">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6955,10 +6973,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7147,42 +7165,42 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="G27">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
       <c r="H27">
-        <v>2.1</v>
+        <v>2.98</v>
       </c>
       <c r="I27">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="J27">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7197,10 +7215,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="Q27">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7389,42 +7407,42 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F28">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="G28">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="H28">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="I28">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="J28">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K28">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7439,10 +7457,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7631,42 +7649,42 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F29">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="G29">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="H29">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="I29">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="J29">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7681,10 +7699,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q29">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7873,48 +7891,48 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F30">
-        <v>1.38</v>
+        <v>3.45</v>
       </c>
       <c r="G30">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="H30">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="I30">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="J30">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -7923,10 +7941,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q30">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -7947,112 +7965,112 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -8115,72 +8133,72 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F31">
+        <v>2.82</v>
+      </c>
+      <c r="G31">
         <v>3.2</v>
       </c>
-      <c r="G31">
-        <v>3.3</v>
-      </c>
       <c r="H31">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I31">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J31">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K31">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="R31">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -8189,175 +8207,175 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BG31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8365,241 +8383,725 @@
         <v>90</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F32">
+        <v>2.1</v>
+      </c>
+      <c r="G32">
+        <v>2.38</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>3.55</v>
+      </c>
+      <c r="J32">
+        <v>3.75</v>
+      </c>
+      <c r="K32">
+        <v>4.5</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>2.36</v>
+      </c>
+      <c r="Q32">
+        <v>1.58</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>28</v>
+      </c>
+      <c r="Y32">
+        <v>22</v>
+      </c>
+      <c r="Z32">
+        <v>32</v>
+      </c>
+      <c r="AA32">
+        <v>65</v>
+      </c>
+      <c r="AB32">
+        <v>17</v>
+      </c>
+      <c r="AC32">
+        <v>12</v>
+      </c>
+      <c r="AD32">
+        <v>17.5</v>
+      </c>
+      <c r="AE32">
+        <v>40</v>
+      </c>
+      <c r="AF32">
+        <v>21</v>
+      </c>
+      <c r="AG32">
+        <v>14</v>
+      </c>
+      <c r="AH32">
+        <v>18.5</v>
+      </c>
+      <c r="AI32">
+        <v>44</v>
+      </c>
+      <c r="AJ32">
+        <v>36</v>
+      </c>
+      <c r="AK32">
+        <v>26</v>
+      </c>
+      <c r="AL32">
+        <v>36</v>
+      </c>
+      <c r="AM32">
+        <v>75</v>
+      </c>
+      <c r="AN32">
+        <v>14</v>
+      </c>
+      <c r="AO32">
+        <v>27</v>
+      </c>
+      <c r="AP32">
+        <v>16.5</v>
+      </c>
+      <c r="AQ32">
+        <v>13</v>
+      </c>
+      <c r="AR32">
+        <v>19</v>
+      </c>
+      <c r="AS32">
+        <v>4</v>
+      </c>
+      <c r="AT32">
+        <v>10</v>
+      </c>
+      <c r="AU32">
+        <v>7.2</v>
+      </c>
+      <c r="AV32">
+        <v>10.5</v>
+      </c>
+      <c r="AW32">
+        <v>3.85</v>
+      </c>
+      <c r="AX32">
+        <v>12.5</v>
+      </c>
+      <c r="AY32">
+        <v>8.4</v>
+      </c>
+      <c r="AZ32">
+        <v>11</v>
+      </c>
+      <c r="BA32">
+        <v>3.85</v>
+      </c>
+      <c r="BB32">
+        <v>20</v>
+      </c>
+      <c r="BC32">
+        <v>15</v>
+      </c>
+      <c r="BD32">
+        <v>20</v>
+      </c>
+      <c r="BE32">
+        <v>4</v>
+      </c>
+      <c r="BF32">
+        <v>8.6</v>
+      </c>
+      <c r="BG32">
+        <v>16</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33">
+        <v>3.2</v>
+      </c>
+      <c r="G33">
+        <v>3.3</v>
+      </c>
+      <c r="H33">
+        <v>2.38</v>
+      </c>
+      <c r="I33">
+        <v>2.4</v>
+      </c>
+      <c r="J33">
+        <v>3.65</v>
+      </c>
+      <c r="K33">
+        <v>3.7</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>1.06</v>
+      </c>
+      <c r="N33">
+        <v>4.1</v>
+      </c>
+      <c r="O33">
+        <v>1.29</v>
+      </c>
+      <c r="P33">
+        <v>2.08</v>
+      </c>
+      <c r="Q33">
+        <v>1.89</v>
+      </c>
+      <c r="R33">
+        <v>1.4</v>
+      </c>
+      <c r="S33">
+        <v>3.3</v>
+      </c>
+      <c r="T33">
+        <v>1.71</v>
+      </c>
+      <c r="U33">
+        <v>2.32</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>16</v>
+      </c>
+      <c r="Y33">
+        <v>11.5</v>
+      </c>
+      <c r="Z33">
+        <v>16</v>
+      </c>
+      <c r="AA33">
+        <v>34</v>
+      </c>
+      <c r="AB33">
+        <v>14</v>
+      </c>
+      <c r="AC33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33">
+        <v>11</v>
+      </c>
+      <c r="AE33">
+        <v>25</v>
+      </c>
+      <c r="AF33">
+        <v>24</v>
+      </c>
+      <c r="AG33">
+        <v>14</v>
+      </c>
+      <c r="AH33">
+        <v>17</v>
+      </c>
+      <c r="AI33">
+        <v>38</v>
+      </c>
+      <c r="AJ33">
+        <v>60</v>
+      </c>
+      <c r="AK33">
+        <v>38</v>
+      </c>
+      <c r="AL33">
+        <v>48</v>
+      </c>
+      <c r="AM33">
+        <v>90</v>
+      </c>
+      <c r="AN33">
+        <v>32</v>
+      </c>
+      <c r="AO33">
+        <v>18.5</v>
+      </c>
+      <c r="AP33">
+        <v>14.5</v>
+      </c>
+      <c r="AQ33">
+        <v>10</v>
+      </c>
+      <c r="AR33">
+        <v>14</v>
+      </c>
+      <c r="AS33">
+        <v>20</v>
+      </c>
+      <c r="AT33">
+        <v>12</v>
+      </c>
+      <c r="AU33">
+        <v>7.4</v>
+      </c>
+      <c r="AV33">
+        <v>10</v>
+      </c>
+      <c r="AW33">
+        <v>21</v>
+      </c>
+      <c r="AX33">
+        <v>19.5</v>
+      </c>
+      <c r="AY33">
+        <v>11.5</v>
+      </c>
+      <c r="AZ33">
+        <v>15</v>
+      </c>
+      <c r="BA33">
+        <v>29</v>
+      </c>
+      <c r="BB33">
+        <v>28</v>
+      </c>
+      <c r="BC33">
+        <v>22</v>
+      </c>
+      <c r="BD33">
+        <v>36</v>
+      </c>
+      <c r="BE33">
+        <v>29</v>
+      </c>
+      <c r="BF33">
+        <v>26</v>
+      </c>
+      <c r="BG33">
+        <v>15.5</v>
+      </c>
+      <c r="BH33">
+        <v>4.1</v>
+      </c>
+      <c r="BI33">
+        <v>2.82</v>
+      </c>
+      <c r="BJ33">
+        <v>11.5</v>
+      </c>
+      <c r="BK33">
+        <v>3.3</v>
+      </c>
+      <c r="BL33">
+        <v>130</v>
+      </c>
+      <c r="BM33">
+        <v>4.5</v>
+      </c>
+      <c r="BN33">
+        <v>7.8</v>
+      </c>
+      <c r="BO33">
+        <v>4.9</v>
+      </c>
+      <c r="BP33">
+        <v>32</v>
+      </c>
+      <c r="BQ33">
+        <v>4.1</v>
+      </c>
+      <c r="BR33">
+        <v>42</v>
+      </c>
+      <c r="BS33">
+        <v>4.2</v>
+      </c>
+      <c r="BT33">
+        <v>6.4</v>
+      </c>
+      <c r="BU33">
+        <v>4.1</v>
+      </c>
+      <c r="BV33">
+        <v>21</v>
+      </c>
+      <c r="BW33">
+        <v>3.85</v>
+      </c>
+      <c r="BX33">
+        <v>36</v>
+      </c>
+      <c r="BY33">
+        <v>4.1</v>
+      </c>
+      <c r="BZ33">
+        <v>29</v>
+      </c>
+      <c r="CA33">
+        <v>4</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" t="s">
+        <v>174</v>
+      </c>
+      <c r="F34">
         <v>1.04</v>
       </c>
-      <c r="G32">
+      <c r="G34">
         <v>600</v>
       </c>
-      <c r="H32">
+      <c r="H34">
         <v>1.04</v>
       </c>
-      <c r="I32">
+      <c r="I34">
         <v>870</v>
       </c>
-      <c r="J32">
+      <c r="J34">
         <v>1.09</v>
       </c>
-      <c r="K32">
+      <c r="K34">
         <v>950</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
         <v>1.24</v>
       </c>
-      <c r="Q32">
+      <c r="Q34">
         <v>1.01</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32">
-        <v>0</v>
-      </c>
-      <c r="BE32">
-        <v>0</v>
-      </c>
-      <c r="BF32">
-        <v>0</v>
-      </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32">
-        <v>0</v>
-      </c>
-      <c r="BJ32">
-        <v>0</v>
-      </c>
-      <c r="BK32">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>0</v>
-      </c>
-      <c r="BM32">
-        <v>0</v>
-      </c>
-      <c r="BN32">
-        <v>0</v>
-      </c>
-      <c r="BO32">
-        <v>0</v>
-      </c>
-      <c r="BP32">
-        <v>0</v>
-      </c>
-      <c r="BQ32">
-        <v>0</v>
-      </c>
-      <c r="BR32">
-        <v>0</v>
-      </c>
-      <c r="BS32">
-        <v>0</v>
-      </c>
-      <c r="BT32">
-        <v>0</v>
-      </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
-      <c r="BV32">
-        <v>0</v>
-      </c>
-      <c r="BW32">
-        <v>0</v>
-      </c>
-      <c r="BX32">
-        <v>0</v>
-      </c>
-      <c r="BY32">
-        <v>0</v>
-      </c>
-      <c r="BZ32">
-        <v>0</v>
-      </c>
-      <c r="CA32">
-        <v>0</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>169</v>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <v>0</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>0</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
